--- a/SubRES_Tmpl/SubRES_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F0CC4A9-F3F2-4E03-A772-3A071819D0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D40553B-E69F-410D-B8D8-70979510626E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12773" activeTab="4" xr2:uid="{C2ED0186-C1D2-4273-BF02-777941AD8D6C}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="4" xr2:uid="{DC9BE42A-B033-48BD-8326-1D0933A86D98}"/>
   </bookViews>
   <sheets>
     <sheet name="conventional" sheetId="2" r:id="rId1"/>
@@ -1648,10 +1648,10 @@
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
     <cellStyle name="Neutral" xfId="6" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="7" xr:uid="{978EB8C8-138F-4902-90BA-EC08D577E009}"/>
-    <cellStyle name="Normal 3 2" xfId="8" xr:uid="{C8FB5730-0078-486F-89A5-C78751151309}"/>
-    <cellStyle name="Normal 4" xfId="9" xr:uid="{77AC0397-545A-46F1-88BB-B76A1CB1E40C}"/>
-    <cellStyle name="Percent 4" xfId="10" xr:uid="{172FBBB2-34D1-4A6A-98FB-5900DA22F4A1}"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{F419CC3D-2187-4857-9B57-5A3BE85C085A}"/>
+    <cellStyle name="Normal 3 2" xfId="8" xr:uid="{8A114FD9-324C-4F78-8B26-D96C7C90F85B}"/>
+    <cellStyle name="Normal 4" xfId="9" xr:uid="{8B70C87D-11CA-4038-8AC7-960A154118DD}"/>
+    <cellStyle name="Percent 4" xfId="10" xr:uid="{A6AD0FD8-525D-4989-AD30-5283DC99FD8A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2059,7 +2059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CE62C5-D63B-42D2-B232-92EAD4E84DC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67373E67-F7E2-4FEA-8BEF-CD587ED89898}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -5543,7 +5543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90ABE0DB-DD82-4A83-805B-0EB72B18653A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17778B78-A279-4DD9-BBE5-AABCE6D8589B}">
   <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -6829,7 +6829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03340072-4ACD-4A88-B17D-DA636559734B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3DE6B4-328B-435D-B96D-CC63DB4EDE3E}">
   <dimension ref="B3:Y8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -7099,7 +7099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1FF686-D16E-4958-98F8-7FCE52FB7AD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA47DC2-0751-4575-99C2-627C9C2F8DEE}">
   <dimension ref="B2:W61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
@@ -8335,7 +8335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC52D98-BF34-4B15-B43D-E9D7E5DA6C28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C4D062-95AD-4929-A7F7-25E61E5AA483}">
   <dimension ref="B11:V29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>

--- a/SubRES_Tmpl/SubRES_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D40553B-E69F-410D-B8D8-70979510626E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13094D65-F2CF-4A63-9919-291D4EB2A3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="4" xr2:uid="{DC9BE42A-B033-48BD-8326-1D0933A86D98}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12772" activeTab="4" xr2:uid="{C1544003-23DF-49B7-9B3F-8CB989A07E73}"/>
   </bookViews>
   <sheets>
     <sheet name="conventional" sheetId="2" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="212">
   <si>
     <t>~fi_t: UP</t>
   </si>
@@ -1648,10 +1648,10 @@
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
     <cellStyle name="Neutral" xfId="6" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="7" xr:uid="{F419CC3D-2187-4857-9B57-5A3BE85C085A}"/>
-    <cellStyle name="Normal 3 2" xfId="8" xr:uid="{8A114FD9-324C-4F78-8B26-D96C7C90F85B}"/>
-    <cellStyle name="Normal 4" xfId="9" xr:uid="{8B70C87D-11CA-4038-8AC7-960A154118DD}"/>
-    <cellStyle name="Percent 4" xfId="10" xr:uid="{A6AD0FD8-525D-4989-AD30-5283DC99FD8A}"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{CB6AB546-5FB3-4195-8A3D-5F70CDAD02E1}"/>
+    <cellStyle name="Normal 3 2" xfId="8" xr:uid="{318455A4-5879-4986-92A3-D9AA8BC122C8}"/>
+    <cellStyle name="Normal 4" xfId="9" xr:uid="{08F1734E-3440-491C-8CFB-D3FA79F03186}"/>
+    <cellStyle name="Percent 4" xfId="10" xr:uid="{4F3BCCE8-ACA9-4437-AFB0-B5CE45EE4BD5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2059,7 +2059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67373E67-F7E2-4FEA-8BEF-CD587ED89898}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72134D48-C650-4DD0-97FE-C319B4888282}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -2223,13 +2223,13 @@
         <v>14</v>
       </c>
       <c r="F13">
-        <v>0.58899999999999997</v>
+        <v>2.1204000000000001</v>
       </c>
       <c r="I13">
-        <v>0.54400000000000004</v>
+        <v>1.9583999999999999</v>
       </c>
       <c r="L13">
-        <v>0.497</v>
+        <v>1.7891999999999999</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
@@ -2499,13 +2499,13 @@
         <v>14</v>
       </c>
       <c r="F19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="I19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="L19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="M19" t="s">
         <v>23</v>
@@ -2775,13 +2775,13 @@
         <v>38</v>
       </c>
       <c r="E25">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="H25">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="L25">
-        <v>1.2</v>
+        <v>4.32</v>
       </c>
       <c r="M25" t="s">
         <v>23</v>
@@ -2799,7 +2799,7 @@
         <v>18</v>
       </c>
       <c r="T25" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="U25" t="s">
         <v>20</v>
@@ -2840,7 +2840,7 @@
         <v>18</v>
       </c>
       <c r="T26" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="U26" t="s">
         <v>20</v>
@@ -3043,13 +3043,13 @@
         <v>48</v>
       </c>
       <c r="F33">
-        <v>1.294</v>
+        <v>4.6584000000000003</v>
       </c>
       <c r="I33">
-        <v>1.1060000000000001</v>
+        <v>3.9815999999999998</v>
       </c>
       <c r="L33">
-        <v>0.98899999999999999</v>
+        <v>3.5604</v>
       </c>
       <c r="M33" t="s">
         <v>23</v>
@@ -3211,13 +3211,13 @@
         <v>14</v>
       </c>
       <c r="F39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="I39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="L39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -3379,13 +3379,13 @@
         <v>14</v>
       </c>
       <c r="F45">
-        <v>2.5499999999999998</v>
+        <v>9.18</v>
       </c>
       <c r="I45">
-        <v>2.4420000000000002</v>
+        <v>8.7911999999999999</v>
       </c>
       <c r="L45">
-        <v>2.3170000000000002</v>
+        <v>8.3412000000000006</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -3547,13 +3547,13 @@
         <v>14</v>
       </c>
       <c r="F51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="I51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="L51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -3860,10 +3860,10 @@
         <v>14</v>
       </c>
       <c r="I62">
-        <v>0.77800000000000002</v>
+        <v>2.8008000000000002</v>
       </c>
       <c r="L62">
-        <v>0.77800000000000002</v>
+        <v>2.8008000000000002</v>
       </c>
       <c r="M62" t="s">
         <v>23</v>
@@ -4014,19 +4014,19 @@
         <v>14</v>
       </c>
       <c r="H67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="I67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="J67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="K67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="L67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="M67" t="s">
         <v>23</v>
@@ -4165,13 +4165,13 @@
         <v>14</v>
       </c>
       <c r="F72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="I72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="L72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="M72" t="s">
         <v>23</v>
@@ -4356,13 +4356,13 @@
         <v>38</v>
       </c>
       <c r="E79">
-        <v>0.8</v>
+        <v>2.88</v>
       </c>
       <c r="H79">
-        <v>0.8</v>
+        <v>2.88</v>
       </c>
       <c r="L79">
-        <v>0.8</v>
+        <v>2.88</v>
       </c>
       <c r="M79" t="s">
         <v>23</v>
@@ -4570,13 +4570,13 @@
         <v>38</v>
       </c>
       <c r="E87">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="L87">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="M87" t="s">
         <v>23</v>
@@ -4738,13 +4738,13 @@
         <v>38</v>
       </c>
       <c r="E93">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="H93">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="L93">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="M93" t="s">
         <v>23</v>
@@ -4853,9 +4853,6 @@
       <c r="B97" t="s">
         <v>43</v>
       </c>
-      <c r="C97" t="s">
-        <v>14</v>
-      </c>
       <c r="D97" t="s">
         <v>38</v>
       </c>
@@ -4882,9 +4879,6 @@
       <c r="B98" t="s">
         <v>43</v>
       </c>
-      <c r="C98" t="s">
-        <v>14</v>
-      </c>
       <c r="D98" t="s">
         <v>38</v>
       </c>
@@ -4911,26 +4905,23 @@
       <c r="B99" t="s">
         <v>43</v>
       </c>
-      <c r="C99" t="s">
-        <v>14</v>
-      </c>
       <c r="D99" t="s">
         <v>38</v>
       </c>
       <c r="G99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M99" t="s">
         <v>23</v>
@@ -4940,9 +4931,6 @@
       <c r="B100" t="s">
         <v>43</v>
       </c>
-      <c r="C100" t="s">
-        <v>14</v>
-      </c>
       <c r="D100" t="s">
         <v>38</v>
       </c>
@@ -4969,9 +4957,6 @@
       <c r="B101" t="s">
         <v>43</v>
       </c>
-      <c r="C101" t="s">
-        <v>14</v>
-      </c>
       <c r="D101" t="s">
         <v>38</v>
       </c>
@@ -5007,9 +4992,6 @@
       <c r="B102" t="s">
         <v>43</v>
       </c>
-      <c r="C102" t="s">
-        <v>14</v>
-      </c>
       <c r="D102" t="s">
         <v>38</v>
       </c>
@@ -5045,9 +5027,6 @@
       <c r="B103" t="s">
         <v>44</v>
       </c>
-      <c r="C103" t="s">
-        <v>14</v>
-      </c>
       <c r="D103" t="s">
         <v>38</v>
       </c>
@@ -5074,9 +5053,6 @@
       <c r="B104" t="s">
         <v>44</v>
       </c>
-      <c r="C104" t="s">
-        <v>14</v>
-      </c>
       <c r="D104" t="s">
         <v>38</v>
       </c>
@@ -5103,26 +5079,23 @@
       <c r="B105" t="s">
         <v>44</v>
       </c>
-      <c r="C105" t="s">
-        <v>14</v>
-      </c>
       <c r="D105" t="s">
         <v>38</v>
       </c>
       <c r="G105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M105" t="s">
         <v>23</v>
@@ -5132,9 +5105,6 @@
       <c r="B106" t="s">
         <v>44</v>
       </c>
-      <c r="C106" t="s">
-        <v>14</v>
-      </c>
       <c r="D106" t="s">
         <v>38</v>
       </c>
@@ -5161,9 +5131,6 @@
       <c r="B107" t="s">
         <v>44</v>
       </c>
-      <c r="C107" t="s">
-        <v>14</v>
-      </c>
       <c r="D107" t="s">
         <v>38</v>
       </c>
@@ -5199,9 +5166,6 @@
       <c r="B108" t="s">
         <v>44</v>
       </c>
-      <c r="C108" t="s">
-        <v>14</v>
-      </c>
       <c r="D108" t="s">
         <v>38</v>
       </c>
@@ -5358,28 +5322,28 @@
         <v>53</v>
       </c>
       <c r="E112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="F112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="G112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="H112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="I112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="J112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="K112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="L112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="M112" t="s">
         <v>23</v>
@@ -5543,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17778B78-A279-4DD9-BBE5-AABCE6D8589B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0668CC4E-A1C7-4466-A19B-55CC4761902C}">
   <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -6829,7 +6793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3DE6B4-328B-435D-B96D-CC63DB4EDE3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D5A420B-6CA8-4E3E-847C-6082A2C6DB13}">
   <dimension ref="B3:Y8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -7099,7 +7063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA47DC2-0751-4575-99C2-627C9C2F8DEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4292389-4134-4CE8-A82D-8A631C8060C9}">
   <dimension ref="B2:W61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
@@ -8335,7 +8299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C4D062-95AD-4929-A7F7-25E61E5AA483}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEE55EF-D242-474C-945C-154F43D5E9E7}">
   <dimension ref="B11:V29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>

--- a/SubRES_Tmpl/SubRES_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_Conventional.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13094D65-F2CF-4A63-9919-291D4EB2A3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{351B02EA-6B79-4099-81A9-B84A0B7060B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12772" activeTab="4" xr2:uid="{C1544003-23DF-49B7-9B3F-8CB989A07E73}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12772" activeTab="3" xr2:uid="{34306113-F2EF-4BDE-9C38-1E498EE01DFB}"/>
   </bookViews>
   <sheets>
     <sheet name="conventional" sheetId="2" r:id="rId1"/>
     <sheet name="H2 prod" sheetId="3" r:id="rId2"/>
     <sheet name="EV Battery" sheetId="4" r:id="rId3"/>
-    <sheet name="ELC_Storage" sheetId="5" r:id="rId4"/>
-    <sheet name="misc" sheetId="6" r:id="rId5"/>
+    <sheet name="misc" sheetId="5" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
@@ -54,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="214">
   <si>
     <t>~fi_t: UP</t>
   </si>
@@ -74,6 +73,12 @@
     <t>attribute</t>
   </si>
   <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>time_slice</t>
+  </si>
+  <si>
     <t>set</t>
   </si>
   <si>
@@ -92,6 +97,9 @@
     <t>vintage</t>
   </si>
   <si>
+    <t>pcg</t>
+  </si>
+  <si>
     <t>en_gas_ccgt</t>
   </si>
   <si>
@@ -107,6 +115,9 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Natural gas combined cycle. IEA GEC</t>
+  </si>
+  <si>
     <t>GW</t>
   </si>
   <si>
@@ -125,6 +136,9 @@
     <t>en_gas_turbine</t>
   </si>
   <si>
+    <t>Natural gas open-cycle combustion turbine. IEA GEC</t>
+  </si>
+  <si>
     <t>act_cost</t>
   </si>
   <si>
@@ -134,42 +148,72 @@
     <t>en_chp_gas_cc_ext</t>
   </si>
   <si>
+    <t>Gas combined cycle CHP, steam extraction (large). DEA el&amp;dh 05</t>
+  </si>
+  <si>
     <t>efficiency</t>
   </si>
   <si>
     <t>en_gas_ccs</t>
   </si>
   <si>
+    <t>Natural gas CCGT with post-combustion CCS. IEA GEC</t>
+  </si>
+  <si>
     <t>ncap_tlife</t>
   </si>
   <si>
     <t>en_coal_subcritical</t>
   </si>
   <si>
+    <t>Coal subcritical steam cycle. IEA GEC</t>
+  </si>
+  <si>
     <t>ncap_iled</t>
   </si>
   <si>
     <t>en_coal_supercritical</t>
   </si>
   <si>
+    <t>Coal supercritical steam cycle. IEA GEC</t>
+  </si>
+  <si>
     <t>en_coal_ultrasupercritical</t>
   </si>
   <si>
+    <t>Coal ultra-supercritical steam cycle. IEA GEC</t>
+  </si>
+  <si>
     <t>en_coal_igcc</t>
   </si>
   <si>
+    <t>Coal integrated gasification combined cycle. IEA GEC</t>
+  </si>
+  <si>
     <t>en_nuclear</t>
   </si>
   <si>
+    <t>Nuclear large reactor (Gen III/III+). IEA GEC</t>
+  </si>
+  <si>
     <t>en_nuclear_smr</t>
   </si>
   <si>
+    <t>Nuclear small modular reactor. ATB</t>
+  </si>
+  <si>
     <t>en_biomass</t>
   </si>
   <si>
+    <t>Biomass dedicated large-scale. IEA GEC</t>
+  </si>
+  <si>
     <t>en_chp_biomass_chips_ext</t>
   </si>
   <si>
+    <t>Wood-chips CHP, steam extraction (large). DEA el&amp;dh 09a</t>
+  </si>
+  <si>
     <t>HET</t>
   </si>
   <si>
@@ -179,22 +223,55 @@
     <t>en_hop_gas_boiler</t>
   </si>
   <si>
+    <t>Natural gas DH boiler (medium). DEA el&amp;dh 44. Heat capacity basis</t>
+  </si>
+  <si>
     <t>season</t>
   </si>
   <si>
     <t>en_hop_biomass_chips</t>
   </si>
   <si>
+    <t>Wood-chips DH boiler (large). DEA el&amp;dh 09a. Heat capacity basis</t>
+  </si>
+  <si>
     <t>en_hop_electric_boiler</t>
   </si>
   <si>
+    <t>Electric DH boiler (large). DEA el&amp;dh 41. Heat capacity basis; region-uniform</t>
+  </si>
+  <si>
     <t>en_hp_air_10mw</t>
   </si>
   <si>
+    <t>Utility heat pump, air source, 10 MW, 70/35C DH. DEA el&amp;dh 40. heat_efficiency = COP; component split preserved</t>
+  </si>
+  <si>
+    <t>STG</t>
+  </si>
+  <si>
+    <t>en_battery_4h</t>
+  </si>
+  <si>
+    <t>Utility-scale Li-ion battery, 4-hour duration. ATB</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>en_battery_8h</t>
+  </si>
+  <si>
+    <t>Utility-scale Li-ion battery, 8-hour duration. ATB</t>
+  </si>
+  <si>
+    <t>ncap_chpr</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_ccs</t>
   </si>
   <si>
-    <t>ncap_chpr</t>
+    <t>Gas combined cycle CHP with post-combustion CCS. Synthetic (DEA 05 + GEC gas CCS)</t>
   </si>
   <si>
     <t>ncap_ceh</t>
@@ -213,6 +290,30 @@
   </si>
   <si>
     <t>ncap_af</t>
+  </si>
+  <si>
+    <t>stg_eff</t>
+  </si>
+  <si>
+    <t>ncap_afc</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>prc_capact</t>
+  </si>
+  <si>
+    <t>ncap_pkcnt</t>
+  </si>
+  <si>
+    <t>ANNUAL</t>
   </si>
   <si>
     <t>HET,CO2Cap</t>
@@ -376,9 +477,6 @@
     <t>H2prd_Elc_PEM</t>
   </si>
   <si>
-    <t>DAYNITE</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -418,18 +516,9 @@
     <t>ev_battery</t>
   </si>
   <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>STG</t>
-  </si>
-  <si>
     <t>Car battery - 6kw/60Kwh - with V2G (optional)</t>
   </si>
   <si>
-    <t>ACT</t>
-  </si>
-  <si>
     <t>elc_roadtransport</t>
   </si>
   <si>
@@ -475,160 +564,13 @@
     <t>Aux commodity for storage charging</t>
   </si>
   <si>
-    <t>TBTU</t>
+    <t>PJ</t>
   </si>
   <si>
     <t>AuxStoOUT</t>
   </si>
   <si>
     <t>Aux commodity for storage discharging</t>
-  </si>
-  <si>
-    <t>~FI_T: USD21</t>
-  </si>
-  <si>
-    <t>Commodity</t>
-  </si>
-  <si>
-    <t>time_slice</t>
-  </si>
-  <si>
-    <t>ELE,STG</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL</t>
-  </si>
-  <si>
-    <t>8 hour battery - NREL</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL</t>
-  </si>
-  <si>
-    <t>ANNUAL</t>
-  </si>
-  <si>
-    <t>4 hour battery - NREL</t>
-  </si>
-  <si>
-    <t>NCAP_AFC</t>
-  </si>
-  <si>
-    <t>NCAP_COST</t>
-  </si>
-  <si>
-    <t>NCAP_FOM</t>
-  </si>
-  <si>
-    <t>NCAP_PKCNT</t>
-  </si>
-  <si>
-    <t>PRC_CAPACT</t>
-  </si>
-  <si>
-    <t>STG_EFF</t>
-  </si>
-  <si>
-    <t>Utility-scale battery storage cost projections from NREL ATB 2024</t>
-  </si>
-  <si>
-    <t>Includes $100 grid connection cost</t>
-  </si>
-  <si>
-    <t>(2022$)</t>
-  </si>
-  <si>
-    <t>4Hr Battery Storage</t>
-  </si>
-  <si>
-    <t>CAPEX</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>Conservative</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Fixed O&amp;M</t>
-  </si>
-  <si>
-    <t>8Hr Battery Storage</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Roundtrip </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is duration/24 - assume one cycle per day</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VAROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = 0</t>
-    </r>
   </si>
   <si>
     <t>~FI_T: USD25~FX~ACT_BND</t>
@@ -767,14 +709,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -871,45 +811,8 @@
       <sz val="10"/>
       <name val="STKFLOW - 14 of 38"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -997,14 +900,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1203,19 +1100,8 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1225,10 +1111,8 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1622,25 +1506,11 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="9" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="9"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="9" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="17" fillId="16" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="14" fillId="16" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="17" fillId="16" borderId="20" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="5"/>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="9">
     <cellStyle name="Bad" xfId="5" builtinId="27"/>
     <cellStyle name="Good" xfId="4" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -1648,10 +1518,8 @@
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
     <cellStyle name="Neutral" xfId="6" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="7" xr:uid="{CB6AB546-5FB3-4195-8A3D-5F70CDAD02E1}"/>
-    <cellStyle name="Normal 3 2" xfId="8" xr:uid="{318455A4-5879-4986-92A3-D9AA8BC122C8}"/>
-    <cellStyle name="Normal 4" xfId="9" xr:uid="{08F1734E-3440-491C-8CFB-D3FA79F03186}"/>
-    <cellStyle name="Percent 4" xfId="10" xr:uid="{4F3BCCE8-ACA9-4437-AFB0-B5CE45EE4BD5}"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{D4C2EA9A-AD6C-4D65-8DC6-DF3744963A7E}"/>
+    <cellStyle name="Normal 3 2" xfId="8" xr:uid="{F0B9B3DD-12D9-4D14-860C-065C7244DCA7}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2059,19 +1927,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72134D48-C650-4DD0-97FE-C319B4888282}">
-  <dimension ref="B9:U116"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B949F905-A8EB-4CC2-9608-F37A840F2E88}">
+  <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:21">
+    <row r="9" spans="2:25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21">
+      <c r="R9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25">
       <c r="B10" t="s">
         <v>2</v>
       </c>
@@ -2085,224 +1953,248 @@
         <v>2020</v>
       </c>
       <c r="F10">
+        <v>2022</v>
+      </c>
+      <c r="G10">
         <v>2024</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>2025</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>2030</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>2035</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>2040</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>2045</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>2050</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="s">
         <v>7</v>
       </c>
       <c r="R10" t="s">
         <v>8</v>
       </c>
       <c r="S10" t="s">
+        <v>2</v>
+      </c>
+      <c r="T10" t="s">
         <v>9</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>10</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="2:21">
+      <c r="W10" t="s">
+        <v>12</v>
+      </c>
+      <c r="X10" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25">
       <c r="B11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11">
+        <v>17</v>
+      </c>
+      <c r="G11">
         <v>941</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>941</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>941</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" t="s">
+        <v>19</v>
+      </c>
+      <c r="S11" t="s">
         <v>15</v>
       </c>
-      <c r="O11" t="s">
+      <c r="T11" t="s">
+        <v>20</v>
+      </c>
+      <c r="U11" t="s">
+        <v>21</v>
+      </c>
+      <c r="V11" t="s">
+        <v>22</v>
+      </c>
+      <c r="W11" t="s">
+        <v>23</v>
+      </c>
+      <c r="X11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25">
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>16</v>
       </c>
-      <c r="P11" t="s">
-        <v>12</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="D12" t="s">
         <v>17</v>
       </c>
-      <c r="S11" t="s">
-        <v>18</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="G12">
+        <v>23.5</v>
+      </c>
+      <c r="J12">
+        <v>23.5</v>
+      </c>
+      <c r="M12">
+        <v>23.5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="R12" t="s">
         <v>19</v>
       </c>
-      <c r="U11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21">
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12">
-        <v>23.5</v>
-      </c>
-      <c r="I12">
-        <v>23.5</v>
-      </c>
-      <c r="L12">
-        <v>23.5</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="S12" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12" t="s">
         <v>21</v>
       </c>
-      <c r="O12" t="s">
+      <c r="V12" t="s">
+        <v>22</v>
+      </c>
+      <c r="W12" t="s">
+        <v>23</v>
+      </c>
+      <c r="X12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25">
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="P12" t="s">
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>2.1204000000000001</v>
+      </c>
+      <c r="J13">
+        <v>1.9583999999999999</v>
+      </c>
+      <c r="M13">
+        <v>1.7891999999999999</v>
+      </c>
+      <c r="N13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" t="s">
+        <v>30</v>
+      </c>
+      <c r="T13" t="s">
+        <v>31</v>
+      </c>
+      <c r="U13" t="s">
+        <v>21</v>
+      </c>
+      <c r="V13" t="s">
         <v>22</v>
       </c>
-      <c r="R12" t="s">
+      <c r="W13" t="s">
+        <v>23</v>
+      </c>
+      <c r="X13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
         <v>17</v>
       </c>
-      <c r="S12" t="s">
-        <v>18</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="G14">
+        <v>0.59</v>
+      </c>
+      <c r="J14">
+        <v>0.61</v>
+      </c>
+      <c r="M14">
+        <v>0.61</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
         <v>19</v>
       </c>
-      <c r="U12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21">
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13">
-        <v>2.1204000000000001</v>
-      </c>
-      <c r="I13">
-        <v>1.9583999999999999</v>
-      </c>
-      <c r="L13">
-        <v>1.7891999999999999</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="S14" t="s">
+        <v>33</v>
+      </c>
+      <c r="T14" t="s">
+        <v>34</v>
+      </c>
+      <c r="U14" t="s">
+        <v>21</v>
+      </c>
+      <c r="V14" t="s">
+        <v>22</v>
+      </c>
+      <c r="W14" t="s">
         <v>23</v>
       </c>
-      <c r="O13" t="s">
+      <c r="X14" t="s">
         <v>24</v>
       </c>
-      <c r="P13" t="s">
-        <v>25</v>
-      </c>
-      <c r="R13" t="s">
+    </row>
+    <row r="15" spans="2:25">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
         <v>17</v>
-      </c>
-      <c r="S13" t="s">
-        <v>18</v>
-      </c>
-      <c r="T13" t="s">
-        <v>19</v>
-      </c>
-      <c r="U13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21">
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14">
-        <v>0.59</v>
-      </c>
-      <c r="I14">
-        <v>0.61</v>
-      </c>
-      <c r="L14">
-        <v>0.61</v>
-      </c>
-      <c r="M14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" t="s">
-        <v>27</v>
-      </c>
-      <c r="R14" t="s">
-        <v>17</v>
-      </c>
-      <c r="S14" t="s">
-        <v>18</v>
-      </c>
-      <c r="T14" t="s">
-        <v>19</v>
-      </c>
-      <c r="U14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21">
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
       </c>
       <c r="E15">
         <v>30</v>
@@ -2328,37 +2220,43 @@
       <c r="L15">
         <v>30</v>
       </c>
-      <c r="M15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="M15">
+        <v>30</v>
+      </c>
+      <c r="N15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" t="s">
+        <v>37</v>
+      </c>
+      <c r="U15" t="s">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s">
+        <v>22</v>
+      </c>
+      <c r="W15" t="s">
+        <v>23</v>
+      </c>
+      <c r="X15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
         <v>16</v>
       </c>
-      <c r="P15" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="D16" t="s">
         <v>17</v>
-      </c>
-      <c r="S15" t="s">
-        <v>18</v>
-      </c>
-      <c r="T15" t="s">
-        <v>19</v>
-      </c>
-      <c r="U15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21">
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2384,201 +2282,219 @@
       <c r="L16">
         <v>3</v>
       </c>
-      <c r="M16" t="s">
-        <v>30</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16" t="s">
+        <v>38</v>
+      </c>
+      <c r="R16" t="s">
+        <v>19</v>
+      </c>
+      <c r="S16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T16" t="s">
+        <v>40</v>
+      </c>
+      <c r="U16" t="s">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s">
+        <v>22</v>
+      </c>
+      <c r="W16" t="s">
+        <v>23</v>
+      </c>
+      <c r="X16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25">
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="P16" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="D17" t="s">
         <v>17</v>
       </c>
-      <c r="S16" t="s">
+      <c r="G17">
+        <v>470.5</v>
+      </c>
+      <c r="J17">
+        <v>470.5</v>
+      </c>
+      <c r="M17">
+        <v>470.5</v>
+      </c>
+      <c r="N17" t="s">
         <v>18</v>
       </c>
-      <c r="T16" t="s">
+      <c r="R17" t="s">
         <v>19</v>
       </c>
-      <c r="U16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21">
-      <c r="B17" t="s">
+      <c r="S17" t="s">
+        <v>41</v>
+      </c>
+      <c r="T17" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" t="s">
+        <v>21</v>
+      </c>
+      <c r="V17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17">
-        <v>470.5</v>
-      </c>
-      <c r="I17">
-        <v>470.5</v>
-      </c>
-      <c r="L17">
-        <v>470.5</v>
-      </c>
-      <c r="M17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="W17" t="s">
+        <v>23</v>
+      </c>
+      <c r="X17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
         <v>16</v>
       </c>
-      <c r="P17" t="s">
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18">
+        <v>18.8</v>
+      </c>
+      <c r="J18">
+        <v>18.8</v>
+      </c>
+      <c r="M18">
+        <v>18.8</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+      <c r="R18" t="s">
+        <v>19</v>
+      </c>
+      <c r="S18" t="s">
+        <v>43</v>
+      </c>
+      <c r="T18" t="s">
+        <v>44</v>
+      </c>
+      <c r="U18" t="s">
+        <v>21</v>
+      </c>
+      <c r="V18" t="s">
+        <v>22</v>
+      </c>
+      <c r="W18" t="s">
+        <v>23</v>
+      </c>
+      <c r="X18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25">
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19">
+        <v>6.9408000000000003</v>
+      </c>
+      <c r="J19">
+        <v>6.9408000000000003</v>
+      </c>
+      <c r="M19">
+        <v>6.9408000000000003</v>
+      </c>
+      <c r="N19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R19" t="s">
+        <v>19</v>
+      </c>
+      <c r="S19" t="s">
+        <v>45</v>
+      </c>
+      <c r="T19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U19" t="s">
+        <v>21</v>
+      </c>
+      <c r="V19" t="s">
+        <v>22</v>
+      </c>
+      <c r="W19" t="s">
+        <v>23</v>
+      </c>
+      <c r="X19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25">
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>0.41</v>
+      </c>
+      <c r="J20">
+        <v>0.42</v>
+      </c>
+      <c r="M20">
+        <v>0.42</v>
+      </c>
+      <c r="N20" t="s">
         <v>32</v>
       </c>
-      <c r="R17" t="s">
+      <c r="R20" t="s">
+        <v>19</v>
+      </c>
+      <c r="S20" t="s">
+        <v>47</v>
+      </c>
+      <c r="T20" t="s">
+        <v>48</v>
+      </c>
+      <c r="U20" t="s">
+        <v>21</v>
+      </c>
+      <c r="V20" t="s">
+        <v>22</v>
+      </c>
+      <c r="W20" t="s">
+        <v>23</v>
+      </c>
+      <c r="X20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25">
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
         <v>17</v>
-      </c>
-      <c r="S17" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21">
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18">
-        <v>18.8</v>
-      </c>
-      <c r="I18">
-        <v>18.8</v>
-      </c>
-      <c r="L18">
-        <v>18.8</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" t="s">
-        <v>16</v>
-      </c>
-      <c r="P18" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" t="s">
-        <v>17</v>
-      </c>
-      <c r="S18" t="s">
-        <v>18</v>
-      </c>
-      <c r="T18" t="s">
-        <v>19</v>
-      </c>
-      <c r="U18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21">
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19">
-        <v>6.9408000000000003</v>
-      </c>
-      <c r="I19">
-        <v>6.9408000000000003</v>
-      </c>
-      <c r="L19">
-        <v>6.9408000000000003</v>
-      </c>
-      <c r="M19" t="s">
-        <v>23</v>
-      </c>
-      <c r="O19" t="s">
-        <v>16</v>
-      </c>
-      <c r="P19" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S19" t="s">
-        <v>18</v>
-      </c>
-      <c r="T19" t="s">
-        <v>19</v>
-      </c>
-      <c r="U19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="2:21">
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20">
-        <v>0.41</v>
-      </c>
-      <c r="I20">
-        <v>0.42</v>
-      </c>
-      <c r="L20">
-        <v>0.42</v>
-      </c>
-      <c r="M20" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" t="s">
-        <v>16</v>
-      </c>
-      <c r="P20" t="s">
-        <v>35</v>
-      </c>
-      <c r="R20" t="s">
-        <v>17</v>
-      </c>
-      <c r="S20" t="s">
-        <v>18</v>
-      </c>
-      <c r="T20" t="s">
-        <v>19</v>
-      </c>
-      <c r="U20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21">
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
-        <v>14</v>
       </c>
       <c r="E21">
         <v>30</v>
@@ -2604,37 +2520,43 @@
       <c r="L21">
         <v>30</v>
       </c>
-      <c r="M21" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="M21">
+        <v>30</v>
+      </c>
+      <c r="N21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>19</v>
+      </c>
+      <c r="S21" t="s">
+        <v>49</v>
+      </c>
+      <c r="T21" t="s">
+        <v>50</v>
+      </c>
+      <c r="U21" t="s">
+        <v>21</v>
+      </c>
+      <c r="V21" t="s">
+        <v>22</v>
+      </c>
+      <c r="W21" t="s">
+        <v>23</v>
+      </c>
+      <c r="X21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25">
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
         <v>16</v>
       </c>
-      <c r="P21" t="s">
-        <v>36</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="D22" t="s">
         <v>17</v>
-      </c>
-      <c r="S21" t="s">
-        <v>18</v>
-      </c>
-      <c r="T21" t="s">
-        <v>19</v>
-      </c>
-      <c r="U21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="2:21">
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -2660,201 +2582,219 @@
       <c r="L22">
         <v>2</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R22" t="s">
+        <v>29</v>
+      </c>
+      <c r="S22" t="s">
+        <v>51</v>
+      </c>
+      <c r="T22" t="s">
+        <v>52</v>
+      </c>
+      <c r="U22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V22" t="s">
+        <v>22</v>
+      </c>
+      <c r="W22" t="s">
+        <v>23</v>
+      </c>
+      <c r="X22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25">
+      <c r="B23" t="s">
         <v>30</v>
       </c>
-      <c r="O22" t="s">
-        <v>24</v>
-      </c>
-      <c r="P22" t="s">
-        <v>37</v>
-      </c>
-      <c r="R22" t="s">
-        <v>17</v>
-      </c>
-      <c r="S22" t="s">
-        <v>18</v>
-      </c>
-      <c r="T22" t="s">
-        <v>19</v>
-      </c>
-      <c r="U22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21">
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E23">
         <v>967.6</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>912.6</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>879.6</v>
       </c>
-      <c r="M23" t="s">
-        <v>15</v>
-      </c>
-      <c r="O23" t="s">
-        <v>39</v>
-      </c>
-      <c r="P23" t="s">
-        <v>40</v>
+      <c r="N23" t="s">
+        <v>18</v>
       </c>
       <c r="R23" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="S23" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="T23" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="U23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21">
+        <v>21</v>
+      </c>
+      <c r="V23" t="s">
+        <v>22</v>
+      </c>
+      <c r="W23" t="s">
+        <v>57</v>
+      </c>
+      <c r="X23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25">
       <c r="B24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E24">
         <v>32.200000000000003</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>30.6</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>28.6</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+      <c r="R24" t="s">
+        <v>54</v>
+      </c>
+      <c r="S24" t="s">
+        <v>58</v>
+      </c>
+      <c r="T24" t="s">
+        <v>59</v>
+      </c>
+      <c r="U24" t="s">
         <v>21</v>
       </c>
-      <c r="O24" t="s">
-        <v>39</v>
-      </c>
-      <c r="P24" t="s">
-        <v>42</v>
-      </c>
-      <c r="R24" t="s">
-        <v>17</v>
-      </c>
-      <c r="S24" t="s">
-        <v>18</v>
-      </c>
-      <c r="T24" t="s">
-        <v>41</v>
-      </c>
-      <c r="U24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21">
+      <c r="V24" t="s">
+        <v>22</v>
+      </c>
+      <c r="W24" t="s">
+        <v>57</v>
+      </c>
+      <c r="X24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25">
       <c r="B25" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E25">
         <v>4.68</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>4.68</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>4.32</v>
       </c>
-      <c r="M25" t="s">
-        <v>23</v>
-      </c>
-      <c r="O25" t="s">
-        <v>39</v>
-      </c>
-      <c r="P25" t="s">
-        <v>43</v>
+      <c r="N25" t="s">
+        <v>28</v>
       </c>
       <c r="R25" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="S25" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="T25" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="U25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="2:21">
+        <v>21</v>
+      </c>
+      <c r="V25" t="s">
+        <v>22</v>
+      </c>
+      <c r="W25" t="s">
+        <v>57</v>
+      </c>
+      <c r="X25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25">
       <c r="B26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E26">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>0.6</v>
       </c>
-      <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" t="s">
-        <v>39</v>
-      </c>
-      <c r="P26" t="s">
-        <v>44</v>
+      <c r="N26" t="s">
+        <v>32</v>
       </c>
       <c r="R26" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="S26" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="T26" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="U26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21">
+        <v>21</v>
+      </c>
+      <c r="V26" t="s">
+        <v>22</v>
+      </c>
+      <c r="W26" t="s">
+        <v>57</v>
+      </c>
+      <c r="X26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25">
       <c r="B27" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -2880,37 +2820,46 @@
       <c r="L27">
         <v>25</v>
       </c>
-      <c r="M27" t="s">
-        <v>28</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="M27">
+        <v>25</v>
+      </c>
+      <c r="N27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>64</v>
+      </c>
+      <c r="S27" t="s">
+        <v>65</v>
+      </c>
+      <c r="T27" t="s">
+        <v>66</v>
+      </c>
+      <c r="U27" t="s">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s">
+        <v>22</v>
+      </c>
+      <c r="W27" t="s">
+        <v>23</v>
+      </c>
+      <c r="X27" t="s">
         <v>24</v>
       </c>
-      <c r="P27" t="s">
-        <v>45</v>
-      </c>
-      <c r="R27" t="s">
-        <v>17</v>
-      </c>
-      <c r="S27" t="s">
-        <v>18</v>
-      </c>
-      <c r="T27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="2:21">
+      <c r="Y27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25">
       <c r="B28" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -2936,157 +2885,205 @@
       <c r="L28">
         <v>3</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R28" t="s">
+        <v>64</v>
+      </c>
+      <c r="S28" t="s">
+        <v>68</v>
+      </c>
+      <c r="T28" t="s">
+        <v>69</v>
+      </c>
+      <c r="U28" t="s">
+        <v>21</v>
+      </c>
+      <c r="V28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W28" t="s">
+        <v>23</v>
+      </c>
+      <c r="X28" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25">
+      <c r="B29" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="2:21">
-      <c r="B29" t="s">
-        <v>25</v>
-      </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E29">
         <v>0.55559999999999998</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>0.5</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>0.45450000000000002</v>
       </c>
-      <c r="M29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21">
+      <c r="N29" t="s">
+        <v>70</v>
+      </c>
+      <c r="R29" t="s">
+        <v>29</v>
+      </c>
+      <c r="S29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T29" t="s">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s">
+        <v>21</v>
+      </c>
+      <c r="V29" t="s">
+        <v>22</v>
+      </c>
+      <c r="W29" t="s">
+        <v>23</v>
+      </c>
+      <c r="X29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25">
       <c r="B30" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E30">
         <v>0.15</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0.15</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>0.15</v>
       </c>
-      <c r="M30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="2:21">
+      <c r="N30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25">
       <c r="B31" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31">
+        <v>74</v>
+      </c>
+      <c r="G31">
         <v>2917</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>2681.7</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>2446.5</v>
       </c>
-      <c r="M31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21">
+      <c r="N31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25">
       <c r="B32" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32">
+        <v>74</v>
+      </c>
+      <c r="G32">
         <v>70.599999999999994</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>65.900000000000006</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>61.2</v>
       </c>
-      <c r="M32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
+      <c r="N32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
       <c r="B33" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33">
+        <v>74</v>
+      </c>
+      <c r="G33">
         <v>4.6584000000000003</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>3.9815999999999998</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>3.5604</v>
       </c>
-      <c r="M33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13">
+      <c r="N33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
       <c r="B34" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34">
+        <v>74</v>
+      </c>
+      <c r="G34">
         <v>0.52</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0.54</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>0.54</v>
       </c>
-      <c r="M34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13">
+      <c r="N34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
       <c r="B35" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E35">
         <v>30</v>
@@ -3112,19 +3109,22 @@
       <c r="L35">
         <v>30</v>
       </c>
-      <c r="M35" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13">
+      <c r="M35">
+        <v>30</v>
+      </c>
+      <c r="N35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
       <c r="B36" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -3150,111 +3150,114 @@
       <c r="L36">
         <v>4</v>
       </c>
-      <c r="M36" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13">
+      <c r="M36">
+        <v>4</v>
+      </c>
+      <c r="N36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
       <c r="B37" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37">
+        <v>17</v>
+      </c>
+      <c r="G37">
         <v>1599.6</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>1599.6</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>1599.6</v>
       </c>
-      <c r="M37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13">
+      <c r="N37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
       <c r="B38" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38">
+        <v>17</v>
+      </c>
+      <c r="G38">
         <v>42.3</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>42.3</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>42.3</v>
       </c>
-      <c r="M38" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13">
+      <c r="N38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
       <c r="B39" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39">
+        <v>17</v>
+      </c>
+      <c r="G39">
         <v>8.4995999999999992</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>8.4995999999999992</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>8.4995999999999992</v>
       </c>
-      <c r="M39" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13">
+      <c r="N39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
       <c r="B40" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40">
+        <v>17</v>
+      </c>
+      <c r="G40">
         <v>0.39</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>0.39</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>0.39</v>
       </c>
-      <c r="M40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13">
+      <c r="N40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
       <c r="B41" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -3280,19 +3283,22 @@
       <c r="L41">
         <v>40</v>
       </c>
-      <c r="M41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13">
+      <c r="M41">
+        <v>40</v>
+      </c>
+      <c r="N41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
       <c r="B42" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -3318,111 +3324,114 @@
       <c r="L42">
         <v>4</v>
       </c>
-      <c r="M42" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13">
+      <c r="M42">
+        <v>4</v>
+      </c>
+      <c r="N42" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
       <c r="B43" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43">
+        <v>17</v>
+      </c>
+      <c r="G43">
         <v>1881.9</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>1881.9</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>1881.9</v>
       </c>
-      <c r="M43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13">
+      <c r="N43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
       <c r="B44" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44">
+        <v>17</v>
+      </c>
+      <c r="G44">
         <v>56.5</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>56.5</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>56.5</v>
       </c>
-      <c r="M44" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13">
+      <c r="N44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
       <c r="B45" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45">
+        <v>17</v>
+      </c>
+      <c r="G45">
         <v>9.18</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>8.7911999999999999</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>8.3412000000000006</v>
       </c>
-      <c r="M45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13">
+      <c r="N45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
       <c r="B46" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46">
+        <v>17</v>
+      </c>
+      <c r="G46">
         <v>0.43</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>0.43</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>0.43</v>
       </c>
-      <c r="M46" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13">
+      <c r="N46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
       <c r="B47" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E47">
         <v>40</v>
@@ -3448,19 +3457,22 @@
       <c r="L47">
         <v>40</v>
       </c>
-      <c r="M47" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13">
+      <c r="M47">
+        <v>40</v>
+      </c>
+      <c r="N47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
       <c r="B48" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -3486,111 +3498,114 @@
       <c r="L48">
         <v>4</v>
       </c>
-      <c r="M48" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="2:13">
+      <c r="M48">
+        <v>4</v>
+      </c>
+      <c r="N48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14">
       <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49">
+        <v>2070.1</v>
+      </c>
+      <c r="J49">
+        <v>2070.1</v>
+      </c>
+      <c r="M49">
+        <v>2070.1</v>
+      </c>
+      <c r="N49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14">
+      <c r="B50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50">
+        <v>61.2</v>
+      </c>
+      <c r="J50">
+        <v>61.2</v>
+      </c>
+      <c r="M50">
+        <v>61.2</v>
+      </c>
+      <c r="N50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
+      <c r="B51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51">
+        <v>9.5004000000000008</v>
+      </c>
+      <c r="J51">
+        <v>9.5004000000000008</v>
+      </c>
+      <c r="M51">
+        <v>9.5004000000000008</v>
+      </c>
+      <c r="N51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14">
+      <c r="B52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52">
+        <v>0.46</v>
+      </c>
+      <c r="J52">
+        <v>0.47</v>
+      </c>
+      <c r="M52">
+        <v>0.48</v>
+      </c>
+      <c r="N52" t="s">
         <v>32</v>
       </c>
-      <c r="C49" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49">
-        <v>2070.1</v>
-      </c>
-      <c r="I49">
-        <v>2070.1</v>
-      </c>
-      <c r="L49">
-        <v>2070.1</v>
-      </c>
-      <c r="M49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13">
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>49</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50">
-        <v>61.2</v>
-      </c>
-      <c r="I50">
-        <v>61.2</v>
-      </c>
-      <c r="L50">
-        <v>61.2</v>
-      </c>
-      <c r="M50" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13">
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s">
-        <v>49</v>
-      </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-      <c r="F51">
-        <v>9.5004000000000008</v>
-      </c>
-      <c r="I51">
-        <v>9.5004000000000008</v>
-      </c>
-      <c r="L51">
-        <v>9.5004000000000008</v>
-      </c>
-      <c r="M51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13">
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52">
-        <v>0.46</v>
-      </c>
-      <c r="I52">
-        <v>0.47</v>
-      </c>
-      <c r="L52">
-        <v>0.48</v>
-      </c>
-      <c r="M52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="2:13">
+    </row>
+    <row r="53" spans="2:14">
       <c r="B53" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E53">
         <v>40</v>
@@ -3616,19 +3631,22 @@
       <c r="L53">
         <v>40</v>
       </c>
-      <c r="M53" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13">
+      <c r="M53">
+        <v>40</v>
+      </c>
+      <c r="N53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14">
       <c r="B54" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -3654,88 +3672,91 @@
       <c r="L54">
         <v>4</v>
       </c>
-      <c r="M54" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13">
+      <c r="M54">
+        <v>4</v>
+      </c>
+      <c r="N54" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
       <c r="B55" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55">
+        <v>17</v>
+      </c>
+      <c r="G55">
         <v>2352.4</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>2164.1999999999998</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>2164.1999999999998</v>
       </c>
-      <c r="M55" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="2:13">
+      <c r="N55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
       <c r="B56" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56">
+        <v>17</v>
+      </c>
+      <c r="G56">
         <v>84.7</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>75.3</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>75.3</v>
       </c>
-      <c r="M56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" spans="2:13">
+      <c r="N56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
       <c r="B57" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C57" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57">
+        <v>17</v>
+      </c>
+      <c r="G57">
         <v>0.46</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>0.49</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>0.5</v>
       </c>
-      <c r="M57" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13">
+      <c r="N57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
       <c r="B58" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E58">
         <v>40</v>
@@ -3761,19 +3782,22 @@
       <c r="L58">
         <v>40</v>
       </c>
-      <c r="M58" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="2:13">
+      <c r="M58">
+        <v>40</v>
+      </c>
+      <c r="N58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14">
       <c r="B59" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -3799,85 +3823,88 @@
       <c r="L59">
         <v>4</v>
       </c>
-      <c r="M59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13">
+      <c r="M59">
+        <v>4</v>
+      </c>
+      <c r="N59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14">
       <c r="B60" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60">
+        <v>17</v>
+      </c>
+      <c r="G60">
         <v>6210.4</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>4704.8</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>4234.3</v>
       </c>
-      <c r="M60" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="2:13">
+      <c r="N60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14">
       <c r="B61" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61">
+        <v>17</v>
+      </c>
+      <c r="G61">
         <v>155.30000000000001</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>160</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>150.6</v>
       </c>
-      <c r="M61" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="2:13">
+      <c r="N61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14">
       <c r="B62" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62">
+        <v>17</v>
+      </c>
+      <c r="J62">
         <v>2.8008000000000002</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>2.8008000000000002</v>
       </c>
-      <c r="M62" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13">
+      <c r="N62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
       <c r="B63" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E63">
         <v>60</v>
@@ -3903,19 +3930,22 @@
       <c r="L63">
         <v>60</v>
       </c>
-      <c r="M63" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="2:13">
+      <c r="M63">
+        <v>60</v>
+      </c>
+      <c r="N63" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
       <c r="B64" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E64">
         <v>7</v>
@@ -3941,57 +3971,57 @@
       <c r="L64">
         <v>7</v>
       </c>
-      <c r="M64" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13">
+      <c r="M64">
+        <v>7</v>
+      </c>
+      <c r="N64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
       <c r="B65" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65">
+        <v>17</v>
+      </c>
+      <c r="I65">
         <v>10266</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>8364.9</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>6373.8</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>5480.2</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>4884.6000000000004</v>
       </c>
-      <c r="M65" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13">
+      <c r="N65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14">
       <c r="B66" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66">
-        <v>144.69999999999999</v>
+        <v>17</v>
       </c>
       <c r="I66">
         <v>144.69999999999999</v>
       </c>
       <c r="J66">
-        <v>136</v>
+        <v>144.69999999999999</v>
       </c>
       <c r="K66">
         <v>136</v>
@@ -3999,22 +4029,22 @@
       <c r="L66">
         <v>136</v>
       </c>
-      <c r="M66" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13">
+      <c r="M66">
+        <v>136</v>
+      </c>
+      <c r="N66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
       <c r="B67" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67">
-        <v>2.5992000000000002</v>
+        <v>17</v>
       </c>
       <c r="I67">
         <v>2.5992000000000002</v>
@@ -4028,19 +4058,22 @@
       <c r="L67">
         <v>2.5992000000000002</v>
       </c>
-      <c r="M67" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13">
+      <c r="M67">
+        <v>2.5992000000000002</v>
+      </c>
+      <c r="N67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14">
       <c r="B68" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E68">
         <v>40</v>
@@ -4066,19 +4099,22 @@
       <c r="L68">
         <v>40</v>
       </c>
-      <c r="M68" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13">
+      <c r="M68">
+        <v>40</v>
+      </c>
+      <c r="N68" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
       <c r="B69" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -4104,134 +4140,137 @@
       <c r="L69">
         <v>3</v>
       </c>
-      <c r="M69" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13">
+      <c r="M69">
+        <v>3</v>
+      </c>
+      <c r="N69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
       <c r="B70" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C70" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70">
+        <v>17</v>
+      </c>
+      <c r="G70">
         <v>2258.3000000000002</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>2211.3000000000002</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>2164.1999999999998</v>
       </c>
-      <c r="M70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13">
+      <c r="N70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
       <c r="B71" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C71" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71">
+        <v>17</v>
+      </c>
+      <c r="G71">
         <v>80</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>75.3</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>75.3</v>
       </c>
-      <c r="M71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13">
+      <c r="N71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
       <c r="B72" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C72" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="F72">
+        <v>17</v>
+      </c>
+      <c r="G72">
         <v>5.2451999999999996</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>5.2451999999999996</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>5.2451999999999996</v>
       </c>
-      <c r="M72" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13">
+      <c r="N72" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
       <c r="B73" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73">
+        <v>17</v>
+      </c>
+      <c r="G73">
         <v>0.35</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>0.35</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>0.35</v>
       </c>
-      <c r="M73" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13">
+      <c r="N73" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
       <c r="B74" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74">
+        <v>17</v>
+      </c>
+      <c r="G74">
         <v>0.6</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>0.6</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>0.6</v>
       </c>
-      <c r="M74" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" spans="2:13">
+      <c r="N74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
       <c r="B75" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C75" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E75">
         <v>45</v>
@@ -4257,19 +4296,22 @@
       <c r="L75">
         <v>45</v>
       </c>
-      <c r="M75" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="76" spans="2:13">
+      <c r="M75">
+        <v>45</v>
+      </c>
+      <c r="N75" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
       <c r="B76" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -4295,111 +4337,114 @@
       <c r="L76">
         <v>3</v>
       </c>
-      <c r="M76" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13">
+      <c r="M76">
+        <v>3</v>
+      </c>
+      <c r="N76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
       <c r="B77" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C77" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D77" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E77">
         <v>2748.9</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>2638.9</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>2528.9</v>
       </c>
-      <c r="M77" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13">
+      <c r="N77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
       <c r="B78" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E78">
         <v>75.900000000000006</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>70.400000000000006</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>68.2</v>
       </c>
-      <c r="M78" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13">
+      <c r="N78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
       <c r="B79" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E79">
         <v>2.88</v>
       </c>
-      <c r="H79">
+      <c r="I79">
         <v>2.88</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>2.88</v>
       </c>
-      <c r="M79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13">
+      <c r="N79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
       <c r="B80" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C80" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D80" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E80">
         <v>0.40899999999999997</v>
       </c>
-      <c r="H80">
+      <c r="I80">
         <v>0.41</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>0.39400000000000002</v>
       </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13">
+      <c r="N80" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14">
       <c r="B81" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C81" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D81" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E81">
         <v>25</v>
@@ -4425,19 +4470,22 @@
       <c r="L81">
         <v>25</v>
       </c>
-      <c r="M81" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13">
+      <c r="M81">
+        <v>25</v>
+      </c>
+      <c r="N81" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14">
       <c r="B82" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C82" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D82" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -4463,157 +4511,160 @@
       <c r="L82">
         <v>2</v>
       </c>
-      <c r="M82" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13">
+      <c r="M82">
+        <v>2</v>
+      </c>
+      <c r="N82" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14">
       <c r="B83" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C83" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D83" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E83">
         <v>1.8237000000000001</v>
       </c>
-      <c r="H83">
+      <c r="I83">
         <v>1.8137000000000001</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>1.9169</v>
       </c>
-      <c r="M83" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13">
+      <c r="N83" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14">
       <c r="B84" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C84" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E84">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H84">
+      <c r="I84">
         <v>0.14000000000000001</v>
       </c>
-      <c r="L84">
+      <c r="M84">
         <v>0.13</v>
       </c>
-      <c r="M84" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13">
+      <c r="N84" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14">
       <c r="B85" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E85">
         <v>66</v>
       </c>
-      <c r="H85">
+      <c r="I85">
         <v>55</v>
       </c>
-      <c r="L85">
+      <c r="M85">
         <v>55</v>
       </c>
-      <c r="M85" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13">
+      <c r="N85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14">
       <c r="B86" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D86" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E86">
         <v>2.1</v>
       </c>
-      <c r="H86">
+      <c r="I86">
         <v>2.1</v>
       </c>
-      <c r="L86">
+      <c r="M86">
         <v>1.9</v>
       </c>
-      <c r="M86" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="87" spans="2:13">
+      <c r="N86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14">
       <c r="B87" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D87" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E87">
         <v>1.08</v>
       </c>
-      <c r="H87">
+      <c r="I87">
         <v>1.08</v>
       </c>
-      <c r="L87">
+      <c r="M87">
         <v>1.08</v>
       </c>
-      <c r="M87" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="88" spans="2:13">
+      <c r="N87" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14">
       <c r="B88" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E88">
         <v>1.03</v>
       </c>
-      <c r="H88">
+      <c r="I88">
         <v>1.04</v>
       </c>
-      <c r="L88">
+      <c r="M88">
         <v>1.04</v>
       </c>
-      <c r="M88" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="89" spans="2:13">
+      <c r="N88" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14">
       <c r="B89" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E89">
         <v>25</v>
@@ -4639,149 +4690,155 @@
       <c r="L89">
         <v>25</v>
       </c>
-      <c r="M89" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="90" spans="2:13">
+      <c r="M89">
+        <v>25</v>
+      </c>
+      <c r="N89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14">
       <c r="B90" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90" t="s">
         <v>38</v>
       </c>
-      <c r="E90">
-        <v>1</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-      <c r="G90">
-        <v>1</v>
-      </c>
-      <c r="H90">
-        <v>1</v>
-      </c>
-      <c r="I90">
-        <v>1</v>
-      </c>
-      <c r="J90">
-        <v>1</v>
-      </c>
-      <c r="K90">
-        <v>1</v>
-      </c>
-      <c r="L90">
-        <v>1</v>
-      </c>
-      <c r="M90" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="2:13">
+    </row>
+    <row r="91" spans="2:14">
       <c r="B91" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C91" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D91" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E91">
         <v>483.8</v>
       </c>
-      <c r="H91">
+      <c r="I91">
         <v>461.8</v>
       </c>
-      <c r="L91">
+      <c r="M91">
         <v>439.8</v>
       </c>
-      <c r="M91" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="2:13">
+      <c r="N91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="2:14">
       <c r="B92" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C92" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D92" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E92">
         <v>38</v>
       </c>
-      <c r="H92">
+      <c r="I92">
         <v>36.6</v>
       </c>
-      <c r="L92">
+      <c r="M92">
         <v>34.5</v>
       </c>
-      <c r="M92" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13">
+      <c r="N92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="2:14">
       <c r="B93" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C93" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D93" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E93">
         <v>1.44</v>
       </c>
-      <c r="H93">
+      <c r="I93">
         <v>1.44</v>
       </c>
-      <c r="L93">
+      <c r="M93">
         <v>1.44</v>
       </c>
-      <c r="M93" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="2:13">
+      <c r="N93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14">
       <c r="B94" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C94" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D94" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E94">
         <v>1.149</v>
       </c>
-      <c r="H94">
+      <c r="I94">
         <v>1.149</v>
       </c>
-      <c r="L94">
+      <c r="M94">
         <v>1.149</v>
       </c>
-      <c r="M94" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="95" spans="2:13">
+      <c r="N94" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="2:14">
       <c r="B95" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C95" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D95" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E95">
         <v>25</v>
@@ -4807,19 +4864,22 @@
       <c r="L95">
         <v>25</v>
       </c>
-      <c r="M95" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13">
+      <c r="M95">
+        <v>25</v>
+      </c>
+      <c r="N95" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14">
       <c r="B96" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C96" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D96" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -4845,19 +4905,19 @@
       <c r="L96">
         <v>3</v>
       </c>
-      <c r="M96" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="97" spans="2:13">
+      <c r="M96">
+        <v>3</v>
+      </c>
+      <c r="N96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97" spans="2:14">
       <c r="B97" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D97" t="s">
-        <v>38</v>
-      </c>
-      <c r="G97">
-        <v>72.400000000000006</v>
+        <v>53</v>
       </c>
       <c r="H97">
         <v>72.400000000000006</v>
@@ -4868,22 +4928,22 @@
       <c r="J97">
         <v>72.400000000000006</v>
       </c>
-      <c r="L97">
+      <c r="K97">
         <v>72.400000000000006</v>
       </c>
-      <c r="M97" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13">
+      <c r="M97">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="N97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14">
       <c r="B98" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D98" t="s">
-        <v>38</v>
-      </c>
-      <c r="G98">
-        <v>1.2</v>
+        <v>53</v>
       </c>
       <c r="H98">
         <v>1.2</v>
@@ -4894,22 +4954,22 @@
       <c r="J98">
         <v>1.2</v>
       </c>
-      <c r="L98">
+      <c r="K98">
         <v>1.2</v>
       </c>
-      <c r="M98" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13">
+      <c r="M98">
+        <v>1.2</v>
+      </c>
+      <c r="N98" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14">
       <c r="B99" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D99" t="s">
-        <v>38</v>
-      </c>
-      <c r="G99">
-        <v>0.72</v>
+        <v>53</v>
       </c>
       <c r="H99">
         <v>0.72</v>
@@ -4920,22 +4980,22 @@
       <c r="J99">
         <v>0.72</v>
       </c>
-      <c r="L99">
+      <c r="K99">
         <v>0.72</v>
       </c>
-      <c r="M99" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="100" spans="2:13">
+      <c r="M99">
+        <v>0.72</v>
+      </c>
+      <c r="N99" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="2:14">
       <c r="B100" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D100" t="s">
-        <v>38</v>
-      </c>
-      <c r="G100">
-        <v>0.99</v>
+        <v>53</v>
       </c>
       <c r="H100">
         <v>0.99</v>
@@ -4946,19 +5006,22 @@
       <c r="J100">
         <v>0.99</v>
       </c>
-      <c r="L100">
+      <c r="K100">
         <v>0.99</v>
       </c>
-      <c r="M100" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101" spans="2:13">
+      <c r="M100">
+        <v>0.99</v>
+      </c>
+      <c r="N100" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101" spans="2:14">
       <c r="B101" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D101" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E101">
         <v>20</v>
@@ -4984,106 +5047,109 @@
       <c r="L101">
         <v>20</v>
       </c>
-      <c r="M101" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13">
+      <c r="M101">
+        <v>20</v>
+      </c>
+      <c r="N101" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="2:14">
       <c r="B102" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D102" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102" t="s">
         <v>38</v>
       </c>
-      <c r="E102">
-        <v>1</v>
-      </c>
-      <c r="F102">
-        <v>1</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
-      <c r="H102">
-        <v>1</v>
-      </c>
-      <c r="I102">
-        <v>1</v>
-      </c>
-      <c r="J102">
-        <v>1</v>
-      </c>
-      <c r="K102">
-        <v>1</v>
-      </c>
-      <c r="L102">
-        <v>1</v>
-      </c>
-      <c r="M102" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103" spans="2:13">
+    </row>
+    <row r="103" spans="2:14">
       <c r="B103" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D103" t="s">
-        <v>38</v>
-      </c>
-      <c r="G103">
+        <v>53</v>
+      </c>
+      <c r="H103">
         <v>1054.7</v>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>1028.3</v>
       </c>
-      <c r="I103">
+      <c r="J103">
         <v>1002</v>
       </c>
-      <c r="J103">
+      <c r="K103">
         <v>976.9</v>
       </c>
-      <c r="L103">
+      <c r="M103">
         <v>951.9</v>
       </c>
-      <c r="M103" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="104" spans="2:13">
+      <c r="N103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="2:14">
       <c r="B104" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D104" t="s">
-        <v>38</v>
-      </c>
-      <c r="G104">
+        <v>53</v>
+      </c>
+      <c r="H104">
         <v>2.2000000000000002</v>
-      </c>
-      <c r="H104">
-        <v>2.1</v>
       </c>
       <c r="I104">
         <v>2.1</v>
       </c>
       <c r="J104">
+        <v>2.1</v>
+      </c>
+      <c r="K104">
         <v>2</v>
       </c>
-      <c r="L104">
+      <c r="M104">
         <v>2</v>
       </c>
-      <c r="M104" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="2:13">
+      <c r="N104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="2:14">
       <c r="B105" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>38</v>
-      </c>
-      <c r="G105">
-        <v>0.72</v>
+        <v>53</v>
       </c>
       <c r="H105">
         <v>0.72</v>
@@ -5094,22 +5160,22 @@
       <c r="J105">
         <v>0.72</v>
       </c>
-      <c r="L105">
+      <c r="K105">
         <v>0.72</v>
       </c>
-      <c r="M105" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="2:13">
+      <c r="M105">
+        <v>0.72</v>
+      </c>
+      <c r="N105" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="2:14">
       <c r="B106" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D106" t="s">
-        <v>38</v>
-      </c>
-      <c r="G106">
-        <v>2.8</v>
+        <v>53</v>
       </c>
       <c r="H106">
         <v>2.8</v>
@@ -5120,19 +5186,22 @@
       <c r="J106">
         <v>2.8</v>
       </c>
-      <c r="L106">
+      <c r="K106">
+        <v>2.8</v>
+      </c>
+      <c r="M106">
         <v>2.9169999999999998</v>
       </c>
-      <c r="M106" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="107" spans="2:13">
+      <c r="N106" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="107" spans="2:14">
       <c r="B107" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D107" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E107">
         <v>25</v>
@@ -5158,347 +5227,1059 @@
       <c r="L107">
         <v>25</v>
       </c>
-      <c r="M107" t="s">
+      <c r="M107">
+        <v>25</v>
+      </c>
+      <c r="N107" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="2:14">
+      <c r="B108" t="s">
+        <v>62</v>
+      </c>
+      <c r="D108" t="s">
+        <v>53</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="109" spans="2:14">
+      <c r="B109" t="s">
+        <v>65</v>
+      </c>
+      <c r="F109">
+        <v>2100.8000000000002</v>
+      </c>
+      <c r="H109">
+        <v>1390.7</v>
+      </c>
+      <c r="I109">
+        <v>1117.5999999999999</v>
+      </c>
+      <c r="J109">
+        <v>1028.7</v>
+      </c>
+      <c r="K109">
+        <v>939.8</v>
+      </c>
+      <c r="L109">
+        <v>850.9</v>
+      </c>
+      <c r="M109">
+        <v>762</v>
+      </c>
+      <c r="N109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="2:14">
+      <c r="B110" t="s">
+        <v>65</v>
+      </c>
+      <c r="F110">
+        <v>48.2</v>
+      </c>
+      <c r="H110">
+        <v>31</v>
+      </c>
+      <c r="I110">
+        <v>24.5</v>
+      </c>
+      <c r="J110">
+        <v>22.3</v>
+      </c>
+      <c r="K110">
+        <v>20.2</v>
+      </c>
+      <c r="L110">
+        <v>18</v>
+      </c>
+      <c r="M110">
+        <v>15.9</v>
+      </c>
+      <c r="N110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="2:14">
+      <c r="B111" t="s">
+        <v>65</v>
+      </c>
+      <c r="F111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="H111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="I111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="J111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="K111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="L111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="M111">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="N111" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="2:13">
-      <c r="B108" t="s">
-        <v>44</v>
-      </c>
-      <c r="D108" t="s">
+    <row r="112" spans="2:14">
+      <c r="B112" t="s">
+        <v>65</v>
+      </c>
+      <c r="F112">
+        <v>0.86</v>
+      </c>
+      <c r="H112">
+        <v>0.86</v>
+      </c>
+      <c r="I112">
+        <v>0.86</v>
+      </c>
+      <c r="J112">
+        <v>0.86</v>
+      </c>
+      <c r="K112">
+        <v>0.86</v>
+      </c>
+      <c r="L112">
+        <v>0.86</v>
+      </c>
+      <c r="M112">
+        <v>0.86</v>
+      </c>
+      <c r="N112" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="113" spans="2:16">
+      <c r="B113" t="s">
+        <v>65</v>
+      </c>
+      <c r="E113">
+        <v>20</v>
+      </c>
+      <c r="F113">
+        <v>20</v>
+      </c>
+      <c r="G113">
+        <v>20</v>
+      </c>
+      <c r="H113">
+        <v>20</v>
+      </c>
+      <c r="I113">
+        <v>20</v>
+      </c>
+      <c r="J113">
+        <v>20</v>
+      </c>
+      <c r="K113">
+        <v>20</v>
+      </c>
+      <c r="L113">
+        <v>20</v>
+      </c>
+      <c r="M113">
+        <v>20</v>
+      </c>
+      <c r="N113" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16">
+      <c r="B114" t="s">
+        <v>65</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114" t="s">
         <v>38</v>
       </c>
-      <c r="E108">
-        <v>1</v>
-      </c>
-      <c r="F108">
-        <v>1</v>
-      </c>
-      <c r="G108">
-        <v>1</v>
-      </c>
-      <c r="H108">
-        <v>1</v>
-      </c>
-      <c r="I108">
-        <v>1</v>
-      </c>
-      <c r="J108">
-        <v>1</v>
-      </c>
-      <c r="K108">
-        <v>1</v>
-      </c>
-      <c r="L108">
-        <v>1</v>
-      </c>
-      <c r="M108" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="109" spans="2:13">
-      <c r="B109" t="s">
-        <v>45</v>
-      </c>
-      <c r="C109" t="s">
-        <v>13</v>
-      </c>
-      <c r="D109" t="s">
-        <v>53</v>
-      </c>
-      <c r="E109">
+    </row>
+    <row r="115" spans="2:16">
+      <c r="B115" t="s">
+        <v>65</v>
+      </c>
+      <c r="E115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="F115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="G115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="H115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="I115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="J115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="K115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="L115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="M115">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="N115" t="s">
+        <v>80</v>
+      </c>
+      <c r="O115" t="s">
+        <v>81</v>
+      </c>
+      <c r="P115" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="2:16">
+      <c r="B116" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116" t="s">
+        <v>80</v>
+      </c>
+      <c r="O116" t="s">
+        <v>83</v>
+      </c>
+      <c r="P116" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="117" spans="2:16">
+      <c r="B117" t="s">
+        <v>65</v>
+      </c>
+      <c r="E117">
+        <v>8.76</v>
+      </c>
+      <c r="F117">
+        <v>8.76</v>
+      </c>
+      <c r="G117">
+        <v>8.76</v>
+      </c>
+      <c r="H117">
+        <v>8.76</v>
+      </c>
+      <c r="I117">
+        <v>8.76</v>
+      </c>
+      <c r="J117">
+        <v>8.76</v>
+      </c>
+      <c r="K117">
+        <v>8.76</v>
+      </c>
+      <c r="L117">
+        <v>8.76</v>
+      </c>
+      <c r="M117">
+        <v>8.76</v>
+      </c>
+      <c r="N117" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="118" spans="2:16">
+      <c r="B118" t="s">
+        <v>65</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118" t="s">
+        <v>85</v>
+      </c>
+      <c r="P118" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="119" spans="2:16">
+      <c r="B119" t="s">
+        <v>68</v>
+      </c>
+      <c r="F119">
+        <v>3721.6</v>
+      </c>
+      <c r="H119">
+        <v>2436.3000000000002</v>
+      </c>
+      <c r="I119">
+        <v>1940.6</v>
+      </c>
+      <c r="J119">
+        <v>1780.6</v>
+      </c>
+      <c r="K119">
+        <v>1617.6</v>
+      </c>
+      <c r="L119">
+        <v>1457.5</v>
+      </c>
+      <c r="M119">
+        <v>1297.5</v>
+      </c>
+      <c r="N119" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="2:16">
+      <c r="B120" t="s">
+        <v>68</v>
+      </c>
+      <c r="F120">
+        <v>87.3</v>
+      </c>
+      <c r="H120">
+        <v>56.3</v>
+      </c>
+      <c r="I120">
+        <v>44.3</v>
+      </c>
+      <c r="J120">
+        <v>40.4</v>
+      </c>
+      <c r="K120">
+        <v>36.5</v>
+      </c>
+      <c r="L120">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="M120">
+        <v>28.8</v>
+      </c>
+      <c r="N120" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="2:16">
+      <c r="B121" t="s">
+        <v>68</v>
+      </c>
+      <c r="F121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="H121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="I121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="J121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="K121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="L121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="M121">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="N121" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="122" spans="2:16">
+      <c r="B122" t="s">
+        <v>68</v>
+      </c>
+      <c r="F122">
+        <v>0.86</v>
+      </c>
+      <c r="H122">
+        <v>0.86</v>
+      </c>
+      <c r="I122">
+        <v>0.86</v>
+      </c>
+      <c r="J122">
+        <v>0.86</v>
+      </c>
+      <c r="K122">
+        <v>0.86</v>
+      </c>
+      <c r="L122">
+        <v>0.86</v>
+      </c>
+      <c r="M122">
+        <v>0.86</v>
+      </c>
+      <c r="N122" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="123" spans="2:16">
+      <c r="B123" t="s">
+        <v>68</v>
+      </c>
+      <c r="E123">
+        <v>20</v>
+      </c>
+      <c r="F123">
+        <v>20</v>
+      </c>
+      <c r="G123">
+        <v>20</v>
+      </c>
+      <c r="H123">
+        <v>20</v>
+      </c>
+      <c r="I123">
+        <v>20</v>
+      </c>
+      <c r="J123">
+        <v>20</v>
+      </c>
+      <c r="K123">
+        <v>20</v>
+      </c>
+      <c r="L123">
+        <v>20</v>
+      </c>
+      <c r="M123">
+        <v>20</v>
+      </c>
+      <c r="N123" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="124" spans="2:16">
+      <c r="B124" t="s">
+        <v>68</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" spans="2:16">
+      <c r="B125" t="s">
+        <v>68</v>
+      </c>
+      <c r="E125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="F125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="G125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="H125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="I125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="J125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="K125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="L125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="M125">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="N125" t="s">
+        <v>80</v>
+      </c>
+      <c r="O125" t="s">
+        <v>81</v>
+      </c>
+      <c r="P125" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="126" spans="2:16">
+      <c r="B126" t="s">
+        <v>68</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126" t="s">
+        <v>80</v>
+      </c>
+      <c r="O126" t="s">
+        <v>83</v>
+      </c>
+      <c r="P126" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="127" spans="2:16">
+      <c r="B127" t="s">
+        <v>68</v>
+      </c>
+      <c r="E127">
+        <v>8.76</v>
+      </c>
+      <c r="F127">
+        <v>8.76</v>
+      </c>
+      <c r="G127">
+        <v>8.76</v>
+      </c>
+      <c r="H127">
+        <v>8.76</v>
+      </c>
+      <c r="I127">
+        <v>8.76</v>
+      </c>
+      <c r="J127">
+        <v>8.76</v>
+      </c>
+      <c r="K127">
+        <v>8.76</v>
+      </c>
+      <c r="L127">
+        <v>8.76</v>
+      </c>
+      <c r="M127">
+        <v>8.76</v>
+      </c>
+      <c r="N127" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="128" spans="2:16">
+      <c r="B128" t="s">
+        <v>68</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>1</v>
+      </c>
+      <c r="N128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P128" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="129" spans="2:14">
+      <c r="B129" t="s">
+        <v>71</v>
+      </c>
+      <c r="C129" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" t="s">
+        <v>87</v>
+      </c>
+      <c r="E129">
         <v>0.52</v>
       </c>
-      <c r="F109">
+      <c r="F129">
         <v>0.52</v>
       </c>
-      <c r="G109">
+      <c r="G129">
         <v>0.52</v>
       </c>
-      <c r="H109">
+      <c r="H129">
         <v>0.52</v>
       </c>
-      <c r="I109">
+      <c r="I129">
         <v>0.52</v>
       </c>
-      <c r="J109">
+      <c r="J129">
         <v>0.52</v>
       </c>
-      <c r="K109">
+      <c r="K129">
         <v>0.52</v>
       </c>
-      <c r="L109">
+      <c r="L129">
         <v>0.52</v>
       </c>
-      <c r="M109" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13">
-      <c r="B110" t="s">
-        <v>45</v>
-      </c>
-      <c r="C110" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" t="s">
-        <v>53</v>
-      </c>
-      <c r="E110">
+      <c r="M129">
+        <v>0.52</v>
+      </c>
+      <c r="N129" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="2:14">
+      <c r="B130" t="s">
+        <v>71</v>
+      </c>
+      <c r="C130" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" t="s">
+        <v>87</v>
+      </c>
+      <c r="E130">
         <v>2917</v>
       </c>
-      <c r="F110">
+      <c r="F130">
         <v>2917</v>
       </c>
-      <c r="G110">
+      <c r="G130">
         <v>2917</v>
       </c>
-      <c r="H110">
+      <c r="H130">
         <v>2917</v>
       </c>
-      <c r="I110">
+      <c r="I130">
         <v>2917</v>
       </c>
-      <c r="J110">
+      <c r="J130">
         <v>2917</v>
       </c>
-      <c r="K110">
+      <c r="K130">
         <v>2917</v>
       </c>
-      <c r="L110">
+      <c r="L130">
         <v>2917</v>
       </c>
-      <c r="M110" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13">
-      <c r="B111" t="s">
-        <v>45</v>
-      </c>
-      <c r="C111" t="s">
-        <v>13</v>
-      </c>
-      <c r="D111" t="s">
-        <v>53</v>
-      </c>
-      <c r="E111">
+      <c r="M130">
+        <v>2917</v>
+      </c>
+      <c r="N130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="2:14">
+      <c r="B131" t="s">
+        <v>71</v>
+      </c>
+      <c r="C131" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" t="s">
+        <v>87</v>
+      </c>
+      <c r="E131">
         <v>70.599999999999994</v>
       </c>
-      <c r="F111">
+      <c r="F131">
         <v>70.599999999999994</v>
       </c>
-      <c r="G111">
+      <c r="G131">
         <v>70.599999999999994</v>
       </c>
-      <c r="H111">
+      <c r="H131">
         <v>70.599999999999994</v>
       </c>
-      <c r="I111">
+      <c r="I131">
         <v>70.599999999999994</v>
       </c>
-      <c r="J111">
+      <c r="J131">
         <v>70.599999999999994</v>
       </c>
-      <c r="K111">
+      <c r="K131">
         <v>70.599999999999994</v>
       </c>
-      <c r="L111">
+      <c r="L131">
         <v>70.599999999999994</v>
       </c>
-      <c r="M111" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="2:13">
-      <c r="B112" t="s">
-        <v>45</v>
-      </c>
-      <c r="C112" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" t="s">
-        <v>53</v>
-      </c>
-      <c r="E112">
+      <c r="M131">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="N131" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="2:14">
+      <c r="B132" t="s">
+        <v>71</v>
+      </c>
+      <c r="C132" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" t="s">
+        <v>87</v>
+      </c>
+      <c r="E132">
         <v>4.68</v>
       </c>
-      <c r="F112">
+      <c r="F132">
         <v>4.68</v>
       </c>
-      <c r="G112">
+      <c r="G132">
         <v>4.68</v>
       </c>
-      <c r="H112">
+      <c r="H132">
         <v>4.68</v>
       </c>
-      <c r="I112">
+      <c r="I132">
         <v>4.68</v>
       </c>
-      <c r="J112">
+      <c r="J132">
         <v>4.68</v>
       </c>
-      <c r="K112">
+      <c r="K132">
         <v>4.68</v>
       </c>
-      <c r="L112">
+      <c r="L132">
         <v>4.68</v>
       </c>
-      <c r="M112" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="113" spans="2:13">
-      <c r="B113" t="s">
-        <v>45</v>
-      </c>
-      <c r="C113" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" t="s">
-        <v>53</v>
-      </c>
-      <c r="E113">
+      <c r="M132">
+        <v>4.68</v>
+      </c>
+      <c r="N132" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="133" spans="2:14">
+      <c r="B133" t="s">
+        <v>71</v>
+      </c>
+      <c r="C133" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" t="s">
+        <v>87</v>
+      </c>
+      <c r="E133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="F113">
+      <c r="F133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="G113">
+      <c r="G133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="H113">
+      <c r="H133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="I113">
+      <c r="I133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="J113">
+      <c r="J133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="K113">
+      <c r="K133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="L113">
+      <c r="L133">
         <v>0.55559999999999998</v>
       </c>
-      <c r="M113" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="114" spans="2:13">
-      <c r="B114" t="s">
-        <v>45</v>
-      </c>
-      <c r="C114" t="s">
-        <v>13</v>
-      </c>
-      <c r="D114" t="s">
-        <v>53</v>
-      </c>
-      <c r="E114">
+      <c r="M133">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="N133" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="134" spans="2:14">
+      <c r="B134" t="s">
+        <v>71</v>
+      </c>
+      <c r="C134" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" t="s">
+        <v>87</v>
+      </c>
+      <c r="E134">
         <v>0.15</v>
       </c>
-      <c r="F114">
+      <c r="F134">
         <v>0.15</v>
       </c>
-      <c r="G114">
+      <c r="G134">
         <v>0.15</v>
       </c>
-      <c r="H114">
+      <c r="H134">
         <v>0.15</v>
       </c>
-      <c r="I114">
+      <c r="I134">
         <v>0.15</v>
       </c>
-      <c r="J114">
+      <c r="J134">
         <v>0.15</v>
       </c>
-      <c r="K114">
+      <c r="K134">
         <v>0.15</v>
       </c>
-      <c r="L114">
+      <c r="L134">
         <v>0.15</v>
       </c>
-      <c r="M114" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="115" spans="2:13">
-      <c r="B115" t="s">
-        <v>45</v>
-      </c>
-      <c r="C115" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" t="s">
-        <v>53</v>
-      </c>
-      <c r="E115">
+      <c r="M134">
+        <v>0.15</v>
+      </c>
+      <c r="N134" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="135" spans="2:14">
+      <c r="B135" t="s">
+        <v>71</v>
+      </c>
+      <c r="C135" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" t="s">
+        <v>87</v>
+      </c>
+      <c r="E135">
         <v>25</v>
       </c>
-      <c r="F115">
+      <c r="F135">
         <v>25</v>
       </c>
-      <c r="G115">
+      <c r="G135">
         <v>25</v>
       </c>
-      <c r="H115">
+      <c r="H135">
         <v>25</v>
       </c>
-      <c r="I115">
+      <c r="I135">
         <v>25</v>
       </c>
-      <c r="J115">
+      <c r="J135">
         <v>25</v>
       </c>
-      <c r="K115">
+      <c r="K135">
         <v>25</v>
       </c>
-      <c r="L115">
+      <c r="L135">
         <v>25</v>
       </c>
-      <c r="M115" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="116" spans="2:13">
-      <c r="B116" t="s">
-        <v>45</v>
-      </c>
-      <c r="C116" t="s">
-        <v>13</v>
-      </c>
-      <c r="D116" t="s">
-        <v>53</v>
-      </c>
-      <c r="E116">
+      <c r="M135">
+        <v>25</v>
+      </c>
+      <c r="N135" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="136" spans="2:14">
+      <c r="B136" t="s">
+        <v>71</v>
+      </c>
+      <c r="C136" t="s">
+        <v>16</v>
+      </c>
+      <c r="D136" t="s">
+        <v>87</v>
+      </c>
+      <c r="E136">
         <v>4</v>
       </c>
-      <c r="F116">
+      <c r="F136">
         <v>4</v>
       </c>
-      <c r="G116">
+      <c r="G136">
         <v>4</v>
       </c>
-      <c r="H116">
+      <c r="H136">
         <v>4</v>
       </c>
-      <c r="I116">
+      <c r="I136">
         <v>4</v>
       </c>
-      <c r="J116">
+      <c r="J136">
         <v>4</v>
       </c>
-      <c r="K116">
+      <c r="K136">
         <v>4</v>
       </c>
-      <c r="L116">
+      <c r="L136">
         <v>4</v>
       </c>
-      <c r="M116" t="s">
-        <v>30</v>
+      <c r="M136">
+        <v>4</v>
+      </c>
+      <c r="N136" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -5507,7 +6288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0668CC4E-A1C7-4466-A19B-55CC4761902C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773A53DD-8494-4220-B26F-4016408438C8}">
   <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -5535,20 +6316,20 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="3"/>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -5556,7 +6337,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
@@ -5564,42 +6345,42 @@
     </row>
     <row r="2" spans="1:18">
       <c r="C2" s="6" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K2" s="6" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M2" s="6" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="5"/>
@@ -5659,7 +6440,7 @@
         <v>2030</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="F4" s="9">
         <v>2015</v>
@@ -5668,25 +6449,25 @@
         <v>2030</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="O4" s="13"/>
       <c r="P4" s="5"/>
@@ -5731,7 +6512,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="P5" s="22"/>
       <c r="Q5" s="22"/>
@@ -5775,7 +6556,7 @@
         <v>1.0940000000000001</v>
       </c>
       <c r="O6" s="30" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="P6" s="31"/>
       <c r="Q6" s="31"/>
@@ -5819,7 +6600,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O7" s="21" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
@@ -5863,7 +6644,7 @@
         <v>1.17</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="31"/>
@@ -5907,7 +6688,7 @@
         <v>1.19</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
@@ -5951,7 +6732,7 @@
         <v>1.18</v>
       </c>
       <c r="O10" s="30" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="P10" s="31"/>
       <c r="Q10" s="31"/>
@@ -5995,7 +6776,7 @@
         <v>1.2</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
@@ -6039,7 +6820,7 @@
         <v>0.70799999999999996</v>
       </c>
       <c r="O12" s="30" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="P12" s="31"/>
       <c r="Q12" s="31"/>
@@ -6083,7 +6864,7 @@
         <v>0.72</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="P13" s="22"/>
       <c r="Q13" s="22"/>
@@ -6127,7 +6908,7 @@
         <v>0.01</v>
       </c>
       <c r="O14" s="42" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="P14" s="43"/>
       <c r="Q14" s="43"/>
@@ -6171,7 +6952,7 @@
         <v>0.06</v>
       </c>
       <c r="O15" s="52" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="P15" s="53"/>
       <c r="Q15" s="53"/>
@@ -6215,7 +6996,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="O16" s="62" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="P16" s="63"/>
       <c r="Q16" s="63"/>
@@ -6259,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="52" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="P17" s="53"/>
       <c r="Q17" s="53"/>
@@ -6303,7 +7084,7 @@
         <v>3.056E-2</v>
       </c>
       <c r="O18" s="72" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="P18" s="73"/>
       <c r="Q18" s="73"/>
@@ -6347,7 +7128,7 @@
         <v>0.02</v>
       </c>
       <c r="O19" s="83" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="P19" s="84"/>
       <c r="Q19" s="84"/>
@@ -6391,7 +7172,7 @@
         <v>1.5694083453910281</v>
       </c>
       <c r="O20" s="93" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="P20" s="73"/>
       <c r="Q20" s="73"/>
@@ -6435,7 +7216,7 @@
         <v>0.3</v>
       </c>
       <c r="O21" s="102" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="P21" s="103"/>
       <c r="Q21" s="103"/>
@@ -6479,7 +7260,7 @@
         <v>0.3</v>
       </c>
       <c r="O22" s="112" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="P22" s="113"/>
       <c r="Q22" s="113"/>
@@ -6523,7 +7304,7 @@
         <v>0.20588235294117646</v>
       </c>
       <c r="O23" s="122" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="P23" s="103"/>
       <c r="Q23" s="103"/>
@@ -6531,18 +7312,18 @@
     </row>
     <row r="26" spans="1:26" ht="17.25" thickBot="1">
       <c r="C26" s="123" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="T26" s="123" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="14.65" thickTop="1">
       <c r="A27" s="124" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B27" s="124" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="C27" s="124" t="str">
         <f>C2&amp;"~"&amp;C3</f>
@@ -6573,7 +7354,7 @@
         <v>input~GASNGA~2015</v>
       </c>
       <c r="J27" s="124" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K27" s="124" t="str">
         <f t="shared" si="1"/>
@@ -6592,42 +7373,42 @@
         <v>efficiency~2050</v>
       </c>
       <c r="O27" s="124" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="P27" s="124" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="Q27" s="124" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="T27" s="124" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="U27" s="124" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="V27" s="124" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="W27" s="124" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="X27" s="124" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="Y27" s="124" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="Z27" s="124" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C28" s="125">
         <f>C8</f>
@@ -6668,7 +7449,7 @@
         <v>0.85470085470085477</v>
       </c>
       <c r="O28" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="P28">
         <v>25</v>
@@ -6689,24 +7470,24 @@
         <v>Hydrogen from low temperature water electrolysis PEM centralised - Large scale  (per 1 kW or 1 MWh H2 HHV)</v>
       </c>
       <c r="W28" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="X28" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y28" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C29" s="125">
         <f>C10</f>
@@ -6747,7 +7528,7 @@
         <v>0.84745762711864414</v>
       </c>
       <c r="O29" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="P29">
         <v>25</v>
@@ -6768,16 +7549,16 @@
         <v>Hydrogen from low temperature water electrolysis - Alkaline centralised, large scale  (per 1 kW or 1 MWh H2 HHV)</v>
       </c>
       <c r="W29" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="X29" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y29" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6793,18 +7574,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D5A420B-6CA8-4E3E-847C-6082A2C6DB13}">
-  <dimension ref="B3:Y8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2E835C-3075-4969-8E89-4B2973AA2817}">
+  <dimension ref="B3:Y14"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.86328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1.73046875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.73046875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
@@ -6813,10 +7594,9 @@
     <col min="15" max="15" width="7.9296875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.46484375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="37.9296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.06640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.3984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.3984375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="6.73046875" bestFit="1" customWidth="1"/>
   </cols>
@@ -6829,7 +7609,7 @@
       <c r="F3" s="128"/>
       <c r="G3" s="128"/>
       <c r="H3" s="128" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="I3" s="128"/>
       <c r="J3" s="128"/>
@@ -6841,7 +7621,7 @@
       <c r="P3" s="128"/>
       <c r="Q3" s="128"/>
       <c r="R3" s="128" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="S3" s="128"/>
       <c r="T3" s="128"/>
@@ -6853,25 +7633,25 @@
     </row>
     <row r="4" spans="2:25">
       <c r="B4" s="128" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="I4">
         <v>2030</v>
@@ -6880,58 +7660,58 @@
         <v>0</v>
       </c>
       <c r="K4" s="128" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L4" s="128" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="M4" s="128" t="s">
+        <v>127</v>
+      </c>
+      <c r="N4" s="128" t="s">
         <v>93</v>
       </c>
-      <c r="N4" s="128" t="s">
-        <v>59</v>
-      </c>
       <c r="O4" s="128" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="P4" s="128" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="Q4" s="128"/>
       <c r="R4" s="128" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="S4" s="128" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="T4" s="128" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="U4" s="128" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="V4" s="128" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="W4" s="128" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="X4" s="128" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="Y4" s="128" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K5" s="128">
         <v>0.90249999999999997</v>
@@ -6954,23 +7734,23 @@
       </c>
       <c r="Q5" s="128"/>
       <c r="R5" s="128" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="S5" s="128" t="str">
         <f>B5</f>
         <v>ev_battery</v>
       </c>
       <c r="T5" s="128" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="U5" s="128" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="V5" s="128" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="W5" s="128" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="X5" s="128"/>
       <c r="Y5" s="128"/>
@@ -6978,7 +7758,7 @@
     <row r="6" spans="2:25">
       <c r="B6" s="128"/>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="K6" s="128"/>
       <c r="L6" s="130">
@@ -7001,10 +7781,10 @@
     <row r="7" spans="2:25">
       <c r="B7" s="128"/>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="K7" s="128"/>
       <c r="L7" s="128"/>
@@ -7026,14 +7806,14 @@
       <c r="B8" s="131"/>
       <c r="E8" s="132"/>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
         <v>AuxStoIN</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -7057,1249 +7837,86 @@
       <c r="X8" s="134"/>
       <c r="Y8" s="134"/>
     </row>
+    <row r="11" spans="2:25">
+      <c r="B11" s="135" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+    </row>
+    <row r="12" spans="2:25">
+      <c r="B12" s="135" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="135" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="135" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="135" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="135" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="135" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="135" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="135" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25">
+      <c r="B13" s="135" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="135" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="135" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="135" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="135"/>
+      <c r="G13" s="136" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+    </row>
+    <row r="14" spans="2:25">
+      <c r="C14" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="E14" s="135" t="s">
+        <v>167</v>
+      </c>
+      <c r="F14" s="135"/>
+      <c r="G14" s="136" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4292389-4134-4CE8-A82D-8A631C8060C9}">
-  <dimension ref="B2:W61"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="2" max="2" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:23">
-      <c r="B2" s="135" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-    </row>
-    <row r="3" spans="2:23">
-      <c r="B3" s="135" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="135" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="135" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="135" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="135" t="s">
-        <v>132</v>
-      </c>
-      <c r="H3" s="135" t="s">
-        <v>133</v>
-      </c>
-      <c r="I3" s="135" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="2:23">
-      <c r="B4" s="135" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="135" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="135" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" s="135" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4" s="135"/>
-      <c r="G4" s="136" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-    </row>
-    <row r="5" spans="2:23">
-      <c r="C5" s="135" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="135" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="135" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5" s="135"/>
-      <c r="G5" s="136" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="2:23">
-      <c r="B8" s="136" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
-      <c r="L8" s="137"/>
-      <c r="M8" s="138" t="s">
-        <v>140</v>
-      </c>
-      <c r="O8" s="137"/>
-      <c r="P8" s="137"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="137"/>
-      <c r="S8" s="137"/>
-      <c r="T8" s="137"/>
-      <c r="U8" s="137"/>
-      <c r="V8" s="137"/>
-      <c r="W8" s="137"/>
-    </row>
-    <row r="9" spans="2:23">
-      <c r="B9" s="136" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="136" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="136" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="136" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="136" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="136" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137" t="s">
-        <v>92</v>
-      </c>
-      <c r="J9" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="137" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="137" t="s">
-        <v>141</v>
-      </c>
-      <c r="M9" s="138" t="s">
-        <v>142</v>
-      </c>
-      <c r="N9" s="137">
-        <f>J35</f>
-        <v>2020</v>
-      </c>
-      <c r="O9" s="137">
-        <f t="shared" ref="O9:T9" si="0">K35</f>
-        <v>2025</v>
-      </c>
-      <c r="P9" s="137">
-        <f t="shared" si="0"/>
-        <v>2030</v>
-      </c>
-      <c r="Q9" s="137">
-        <f t="shared" si="0"/>
-        <v>2035</v>
-      </c>
-      <c r="R9" s="137">
-        <f t="shared" si="0"/>
-        <v>2040</v>
-      </c>
-      <c r="S9" s="137">
-        <f t="shared" si="0"/>
-        <v>2045</v>
-      </c>
-      <c r="T9" s="137">
-        <f t="shared" si="0"/>
-        <v>2050</v>
-      </c>
-      <c r="U9" s="137" t="s">
-        <v>90</v>
-      </c>
-      <c r="V9" s="137" t="s">
-        <v>108</v>
-      </c>
-      <c r="W9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="2:23">
-      <c r="B10" s="136" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="136" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="139" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" s="136" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="136" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="136" t="s">
-        <v>104</v>
-      </c>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10" s="137" t="s">
-        <v>125</v>
-      </c>
-      <c r="K10" s="135" t="s">
-        <v>138</v>
-      </c>
-      <c r="L10" s="135" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="137" t="s">
-        <v>147</v>
-      </c>
-      <c r="N10" s="140">
-        <f>1/N17</f>
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="140"/>
-      <c r="T10" s="140"/>
-      <c r="U10" s="137"/>
-      <c r="V10" s="136" t="str">
-        <f>K10</f>
-        <v>AuxStoOUT</v>
-      </c>
-      <c r="W10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:23">
-      <c r="B11" s="136"/>
-      <c r="C11" s="138" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="138" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" s="136" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="136" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="136" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" s="137" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" s="137" t="s">
-        <v>121</v>
-      </c>
-      <c r="L11" s="137" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="137" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" s="140">
-        <f>4/24</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="127"/>
-      <c r="U11" s="136" t="str">
-        <f>L11</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23">
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137" t="s">
-        <v>146</v>
-      </c>
-      <c r="J12" s="137" t="s">
-        <v>149</v>
-      </c>
-      <c r="K12" s="137" t="s">
-        <v>118</v>
-      </c>
-      <c r="L12" s="137"/>
-      <c r="M12" s="138" t="s">
-        <v>104</v>
-      </c>
-      <c r="N12" s="140">
-        <v>1</v>
-      </c>
-      <c r="O12" s="140"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="140"/>
-      <c r="R12" s="140"/>
-      <c r="S12" s="140"/>
-      <c r="T12" s="140"/>
-      <c r="U12" s="137"/>
-      <c r="V12" s="137"/>
-    </row>
-    <row r="13" spans="2:23">
-      <c r="B13" s="136"/>
-      <c r="C13" s="136"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137" t="s">
-        <v>146</v>
-      </c>
-      <c r="J13" s="137" t="s">
-        <v>150</v>
-      </c>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
-      <c r="M13" s="138"/>
-      <c r="N13" s="140">
-        <f>J40</f>
-        <v>1363</v>
-      </c>
-      <c r="O13" s="140">
-        <f t="shared" ref="O13:T13" si="1">K40</f>
-        <v>956</v>
-      </c>
-      <c r="P13" s="140">
-        <f t="shared" si="1"/>
-        <v>784</v>
-      </c>
-      <c r="Q13" s="140">
-        <f t="shared" si="1"/>
-        <v>735</v>
-      </c>
-      <c r="R13" s="140">
-        <f t="shared" si="1"/>
-        <v>686</v>
-      </c>
-      <c r="S13" s="140">
-        <f t="shared" si="1"/>
-        <v>637</v>
-      </c>
-      <c r="T13" s="140">
-        <f t="shared" si="1"/>
-        <v>588</v>
-      </c>
-      <c r="U13" s="137"/>
-      <c r="V13" s="137"/>
-    </row>
-    <row r="14" spans="2:23">
-      <c r="I14" t="s">
-        <v>146</v>
-      </c>
-      <c r="J14" t="s">
-        <v>151</v>
-      </c>
-      <c r="N14" s="127">
-        <f>J44</f>
-        <v>34</v>
-      </c>
-      <c r="O14" s="127">
-        <f t="shared" ref="O14:T14" si="2">K44</f>
-        <v>24</v>
-      </c>
-      <c r="P14" s="127">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="Q14" s="127">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="R14" s="127">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S14" s="127">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="T14" s="127">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="2:23">
-      <c r="I15" t="s">
-        <v>146</v>
-      </c>
-      <c r="J15" t="s">
-        <v>152</v>
-      </c>
-      <c r="M15" t="s">
-        <v>147</v>
-      </c>
-      <c r="N15" s="127">
-        <v>1</v>
-      </c>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127"/>
-      <c r="Q15" s="127"/>
-      <c r="R15" s="127"/>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-    </row>
-    <row r="16" spans="2:23">
-      <c r="I16" t="s">
-        <v>146</v>
-      </c>
-      <c r="J16" t="s">
-        <v>153</v>
-      </c>
-      <c r="N16" s="140">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O16" s="127"/>
-      <c r="P16" s="127"/>
-      <c r="Q16" s="127"/>
-      <c r="R16" s="127"/>
-      <c r="S16" s="127"/>
-      <c r="T16" s="127"/>
-    </row>
-    <row r="17" spans="9:23">
-      <c r="I17" t="s">
-        <v>146</v>
-      </c>
-      <c r="J17" t="s">
-        <v>154</v>
-      </c>
-      <c r="N17" s="127">
-        <v>0.85</v>
-      </c>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="127"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-    </row>
-    <row r="18" spans="9:23">
-      <c r="I18" t="s">
-        <v>144</v>
-      </c>
-      <c r="J18" t="s">
-        <v>125</v>
-      </c>
-      <c r="K18" s="135" t="s">
-        <v>138</v>
-      </c>
-      <c r="L18" s="135" t="s">
-        <v>14</v>
-      </c>
-      <c r="M18" t="s">
-        <v>147</v>
-      </c>
-      <c r="N18" s="140">
-        <f>1/N25</f>
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="O18" s="127"/>
-      <c r="P18" s="127"/>
-      <c r="Q18" s="127"/>
-      <c r="R18" s="127"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="127"/>
-      <c r="U18" s="137"/>
-      <c r="V18" s="136" t="str">
-        <f>K18</f>
-        <v>AuxStoOUT</v>
-      </c>
-      <c r="W18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="9:23">
-      <c r="I19" t="s">
-        <v>144</v>
-      </c>
-      <c r="J19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K19" t="s">
-        <v>121</v>
-      </c>
-      <c r="L19" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" s="127">
-        <f>8/24</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O19" s="127"/>
-      <c r="P19" s="127"/>
-      <c r="Q19" s="127"/>
-      <c r="R19" s="127"/>
-      <c r="S19" s="127"/>
-      <c r="T19" s="127"/>
-      <c r="U19" s="136" t="str">
-        <f>L19</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="20" spans="9:23">
-      <c r="I20" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" t="s">
-        <v>149</v>
-      </c>
-      <c r="K20" t="s">
-        <v>118</v>
-      </c>
-      <c r="M20" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="127">
-        <v>1</v>
-      </c>
-      <c r="O20" s="127"/>
-      <c r="P20" s="127"/>
-      <c r="Q20" s="127"/>
-      <c r="R20" s="127"/>
-      <c r="S20" s="127"/>
-      <c r="T20" s="127"/>
-    </row>
-    <row r="21" spans="9:23">
-      <c r="I21" t="s">
-        <v>144</v>
-      </c>
-      <c r="J21" t="s">
-        <v>150</v>
-      </c>
-      <c r="N21" s="127">
-        <f>J49</f>
-        <v>2470</v>
-      </c>
-      <c r="O21" s="127">
-        <f t="shared" ref="O21:T21" si="3">K49</f>
-        <v>1714</v>
-      </c>
-      <c r="P21" s="127">
-        <f t="shared" si="3"/>
-        <v>1371</v>
-      </c>
-      <c r="Q21" s="127">
-        <f t="shared" si="3"/>
-        <v>1277</v>
-      </c>
-      <c r="R21" s="127">
-        <f t="shared" si="3"/>
-        <v>1183</v>
-      </c>
-      <c r="S21" s="127">
-        <f t="shared" si="3"/>
-        <v>1089</v>
-      </c>
-      <c r="T21" s="127">
-        <f t="shared" si="3"/>
-        <v>995</v>
-      </c>
-    </row>
-    <row r="22" spans="9:23">
-      <c r="I22" t="s">
-        <v>144</v>
-      </c>
-      <c r="J22" t="s">
-        <v>151</v>
-      </c>
-      <c r="N22" s="127">
-        <f>J53</f>
-        <v>62</v>
-      </c>
-      <c r="O22" s="127">
-        <f t="shared" ref="O22:T22" si="4">K53</f>
-        <v>43</v>
-      </c>
-      <c r="P22" s="127">
-        <f t="shared" si="4"/>
-        <v>34</v>
-      </c>
-      <c r="Q22" s="127">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-      <c r="R22" s="127">
-        <f t="shared" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="S22" s="127">
-        <f t="shared" si="4"/>
-        <v>27</v>
-      </c>
-      <c r="T22" s="127">
-        <f t="shared" si="4"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="9:23">
-      <c r="I23" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" t="s">
-        <v>152</v>
-      </c>
-      <c r="M23" t="s">
-        <v>147</v>
-      </c>
-      <c r="N23" s="127">
-        <v>1</v>
-      </c>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="127"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-    </row>
-    <row r="24" spans="9:23">
-      <c r="I24" t="s">
-        <v>144</v>
-      </c>
-      <c r="J24" t="s">
-        <v>153</v>
-      </c>
-      <c r="N24" s="140">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O24" s="127"/>
-      <c r="P24" s="127"/>
-      <c r="Q24" s="127"/>
-      <c r="R24" s="127"/>
-      <c r="S24" s="127"/>
-      <c r="T24" s="127"/>
-    </row>
-    <row r="25" spans="9:23">
-      <c r="I25" t="s">
-        <v>144</v>
-      </c>
-      <c r="J25" t="s">
-        <v>154</v>
-      </c>
-      <c r="N25" s="127">
-        <v>0.85</v>
-      </c>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="127"/>
-    </row>
-    <row r="31" spans="9:23" ht="15.75">
-      <c r="I31" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="142"/>
-      <c r="M31" s="142"/>
-      <c r="N31" s="142"/>
-      <c r="O31" s="142"/>
-      <c r="P31" s="142"/>
-    </row>
-    <row r="32" spans="9:23" ht="15.75">
-      <c r="I32" s="141" t="s">
-        <v>156</v>
-      </c>
-      <c r="J32" s="142"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="142"/>
-      <c r="M32" s="142"/>
-      <c r="N32" s="142"/>
-      <c r="O32" s="142"/>
-      <c r="P32" s="142"/>
-    </row>
-    <row r="33" spans="9:16">
-      <c r="I33" s="143"/>
-      <c r="J33" s="143"/>
-      <c r="K33" s="143"/>
-      <c r="L33" s="143"/>
-      <c r="M33" s="143"/>
-      <c r="N33" s="143"/>
-      <c r="O33" s="143"/>
-      <c r="P33" s="143"/>
-    </row>
-    <row r="34" spans="9:16" ht="15.75">
-      <c r="I34" s="144" t="s">
-        <v>157</v>
-      </c>
-      <c r="J34" s="145"/>
-      <c r="K34" s="145"/>
-      <c r="L34" s="145"/>
-      <c r="M34" s="145"/>
-      <c r="N34" s="145"/>
-      <c r="O34" s="145"/>
-      <c r="P34" s="145"/>
-    </row>
-    <row r="35" spans="9:16" ht="15.75">
-      <c r="I35" s="145"/>
-      <c r="J35" s="145">
-        <v>2020</v>
-      </c>
-      <c r="K35" s="145">
-        <v>2025</v>
-      </c>
-      <c r="L35" s="145">
-        <v>2030</v>
-      </c>
-      <c r="M35" s="145">
-        <v>2035</v>
-      </c>
-      <c r="N35" s="145">
-        <v>2040</v>
-      </c>
-      <c r="O35" s="145">
-        <v>2045</v>
-      </c>
-      <c r="P35" s="145">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="36" spans="9:16" ht="15.75">
-      <c r="I36" s="146" t="s">
-        <v>158</v>
-      </c>
-      <c r="J36" s="145"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="145"/>
-      <c r="N36" s="145"/>
-      <c r="O36" s="145"/>
-      <c r="P36" s="145"/>
-    </row>
-    <row r="37" spans="9:16" ht="15.75">
-      <c r="I37" s="144" t="s">
-        <v>159</v>
-      </c>
-      <c r="J37" s="145"/>
-      <c r="K37" s="145"/>
-      <c r="L37" s="145"/>
-      <c r="M37" s="145"/>
-      <c r="N37" s="145"/>
-      <c r="O37" s="145"/>
-      <c r="P37" s="145"/>
-    </row>
-    <row r="38" spans="9:16" ht="15.75">
-      <c r="I38" s="145" t="s">
-        <v>160</v>
-      </c>
-      <c r="J38" s="147">
-        <v>1363</v>
-      </c>
-      <c r="K38" s="147">
-        <v>839</v>
-      </c>
-      <c r="L38" s="147">
-        <v>566</v>
-      </c>
-      <c r="M38" s="147">
-        <v>512</v>
-      </c>
-      <c r="N38" s="147">
-        <v>454</v>
-      </c>
-      <c r="O38" s="147">
-        <v>400</v>
-      </c>
-      <c r="P38" s="147">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="39" spans="9:16" ht="15.75">
-      <c r="I39" s="145" t="s">
-        <v>161</v>
-      </c>
-      <c r="J39" s="147">
-        <v>1363</v>
-      </c>
-      <c r="K39" s="147">
-        <v>1167</v>
-      </c>
-      <c r="L39" s="147">
-        <v>981</v>
-      </c>
-      <c r="M39" s="147">
-        <v>981</v>
-      </c>
-      <c r="N39" s="147">
-        <v>981</v>
-      </c>
-      <c r="O39" s="147">
-        <v>981</v>
-      </c>
-      <c r="P39" s="147">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="40" spans="9:16" ht="15.75">
-      <c r="I40" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="J40" s="147">
-        <v>1363</v>
-      </c>
-      <c r="K40" s="147">
-        <v>956</v>
-      </c>
-      <c r="L40" s="147">
-        <v>784</v>
-      </c>
-      <c r="M40" s="147">
-        <v>735</v>
-      </c>
-      <c r="N40" s="147">
-        <v>686</v>
-      </c>
-      <c r="O40" s="147">
-        <v>637</v>
-      </c>
-      <c r="P40" s="147">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="41" spans="9:16" ht="15.75">
-      <c r="I41" s="144" t="s">
-        <v>163</v>
-      </c>
-      <c r="J41" s="148"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="148"/>
-      <c r="N41" s="148"/>
-      <c r="O41" s="148"/>
-      <c r="P41" s="148"/>
-    </row>
-    <row r="42" spans="9:16" ht="15.75">
-      <c r="I42" s="145" t="s">
-        <v>160</v>
-      </c>
-      <c r="J42" s="149">
-        <v>34</v>
-      </c>
-      <c r="K42" s="149">
-        <v>21</v>
-      </c>
-      <c r="L42" s="149">
-        <v>14</v>
-      </c>
-      <c r="M42" s="149">
-        <v>13</v>
-      </c>
-      <c r="N42" s="149">
-        <v>11</v>
-      </c>
-      <c r="O42" s="149">
-        <v>10</v>
-      </c>
-      <c r="P42" s="149">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="9:16" ht="15.75">
-      <c r="I43" s="145" t="s">
-        <v>161</v>
-      </c>
-      <c r="J43" s="149">
-        <v>34</v>
-      </c>
-      <c r="K43" s="149">
-        <v>29</v>
-      </c>
-      <c r="L43" s="149">
-        <v>25</v>
-      </c>
-      <c r="M43" s="149">
-        <v>25</v>
-      </c>
-      <c r="N43" s="149">
-        <v>25</v>
-      </c>
-      <c r="O43" s="149">
-        <v>25</v>
-      </c>
-      <c r="P43" s="149">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="9:16" ht="15.75">
-      <c r="I44" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="J44" s="149">
-        <v>34</v>
-      </c>
-      <c r="K44" s="149">
-        <v>24</v>
-      </c>
-      <c r="L44" s="149">
-        <v>20</v>
-      </c>
-      <c r="M44" s="149">
-        <v>18</v>
-      </c>
-      <c r="N44" s="149">
-        <v>17</v>
-      </c>
-      <c r="O44" s="149">
-        <v>16</v>
-      </c>
-      <c r="P44" s="149">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="9:16" ht="15.75">
-      <c r="I45" s="146" t="s">
-        <v>164</v>
-      </c>
-      <c r="J45" s="148"/>
-      <c r="K45" s="148"/>
-      <c r="L45" s="148"/>
-      <c r="M45" s="148"/>
-      <c r="N45" s="148"/>
-      <c r="O45" s="148"/>
-      <c r="P45" s="148"/>
-    </row>
-    <row r="46" spans="9:16" ht="15.75">
-      <c r="I46" s="144" t="s">
-        <v>159</v>
-      </c>
-      <c r="J46" s="148"/>
-      <c r="K46" s="148"/>
-      <c r="L46" s="148"/>
-      <c r="M46" s="148"/>
-      <c r="N46" s="148"/>
-      <c r="O46" s="148"/>
-      <c r="P46" s="148"/>
-    </row>
-    <row r="47" spans="9:16" ht="15.75">
-      <c r="I47" s="145" t="s">
-        <v>160</v>
-      </c>
-      <c r="J47" s="147">
-        <v>2470</v>
-      </c>
-      <c r="K47" s="147">
-        <v>1518</v>
-      </c>
-      <c r="L47" s="147">
-        <v>1024</v>
-      </c>
-      <c r="M47" s="147">
-        <v>927</v>
-      </c>
-      <c r="N47" s="147">
-        <v>822</v>
-      </c>
-      <c r="O47" s="147">
-        <v>724</v>
-      </c>
-      <c r="P47" s="147">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="48" spans="9:16" ht="15.75">
-      <c r="I48" s="145" t="s">
-        <v>161</v>
-      </c>
-      <c r="J48" s="147">
-        <v>2470</v>
-      </c>
-      <c r="K48" s="147">
-        <v>2111</v>
-      </c>
-      <c r="L48" s="147">
-        <v>1754</v>
-      </c>
-      <c r="M48" s="147">
-        <v>1754</v>
-      </c>
-      <c r="N48" s="147">
-        <v>1754</v>
-      </c>
-      <c r="O48" s="147">
-        <v>1754</v>
-      </c>
-      <c r="P48" s="147">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="49" spans="9:16" ht="15.75">
-      <c r="I49" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="J49" s="147">
-        <v>2470</v>
-      </c>
-      <c r="K49" s="147">
-        <v>1714</v>
-      </c>
-      <c r="L49" s="147">
-        <v>1371</v>
-      </c>
-      <c r="M49" s="147">
-        <v>1277</v>
-      </c>
-      <c r="N49" s="147">
-        <v>1183</v>
-      </c>
-      <c r="O49" s="147">
-        <v>1089</v>
-      </c>
-      <c r="P49" s="147">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="50" spans="9:16" ht="15.75">
-      <c r="I50" s="144" t="s">
-        <v>163</v>
-      </c>
-      <c r="J50" s="148"/>
-      <c r="K50" s="148"/>
-      <c r="L50" s="148"/>
-      <c r="M50" s="148"/>
-      <c r="N50" s="148"/>
-      <c r="O50" s="148"/>
-      <c r="P50" s="148"/>
-    </row>
-    <row r="51" spans="9:16" ht="15.75">
-      <c r="I51" s="145" t="s">
-        <v>160</v>
-      </c>
-      <c r="J51" s="149">
-        <v>62</v>
-      </c>
-      <c r="K51" s="149">
-        <v>38</v>
-      </c>
-      <c r="L51" s="149">
-        <v>26</v>
-      </c>
-      <c r="M51" s="149">
-        <v>23</v>
-      </c>
-      <c r="N51" s="149">
-        <v>21</v>
-      </c>
-      <c r="O51" s="149">
-        <v>18</v>
-      </c>
-      <c r="P51" s="149">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="9:16" ht="15.75">
-      <c r="I52" s="145" t="s">
-        <v>161</v>
-      </c>
-      <c r="J52" s="149">
-        <v>62</v>
-      </c>
-      <c r="K52" s="149">
-        <v>53</v>
-      </c>
-      <c r="L52" s="149">
-        <v>44</v>
-      </c>
-      <c r="M52" s="149">
-        <v>44</v>
-      </c>
-      <c r="N52" s="149">
-        <v>44</v>
-      </c>
-      <c r="O52" s="149">
-        <v>44</v>
-      </c>
-      <c r="P52" s="149">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="9:16" ht="15.75">
-      <c r="I53" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="J53" s="149">
-        <v>62</v>
-      </c>
-      <c r="K53" s="149">
-        <v>43</v>
-      </c>
-      <c r="L53" s="149">
-        <v>34</v>
-      </c>
-      <c r="M53" s="149">
-        <v>32</v>
-      </c>
-      <c r="N53" s="149">
-        <v>30</v>
-      </c>
-      <c r="O53" s="149">
-        <v>27</v>
-      </c>
-      <c r="P53" s="149">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="9:16">
-      <c r="I54" s="143"/>
-      <c r="J54" s="143"/>
-      <c r="K54" s="143"/>
-      <c r="L54" s="143"/>
-      <c r="M54" s="143"/>
-      <c r="N54" s="143"/>
-      <c r="O54" s="143"/>
-      <c r="P54" s="143"/>
-    </row>
-    <row r="55" spans="9:16" ht="15.75">
-      <c r="I55" s="142" t="s">
-        <v>165</v>
-      </c>
-      <c r="J55" s="142">
-        <v>0.85</v>
-      </c>
-      <c r="K55" s="142"/>
-      <c r="L55" s="142"/>
-      <c r="M55" s="142"/>
-      <c r="N55" s="142"/>
-      <c r="O55" s="142"/>
-      <c r="P55" s="142"/>
-    </row>
-    <row r="56" spans="9:16" ht="15.75">
-      <c r="I56" s="142" t="s">
-        <v>166</v>
-      </c>
-      <c r="J56" s="142"/>
-      <c r="K56" s="142"/>
-      <c r="L56" s="142"/>
-      <c r="M56" s="142"/>
-      <c r="N56" s="142"/>
-      <c r="O56" s="142"/>
-      <c r="P56" s="142"/>
-    </row>
-    <row r="57" spans="9:16" ht="15.75">
-      <c r="I57" s="142" t="s">
-        <v>167</v>
-      </c>
-      <c r="J57" s="142"/>
-      <c r="K57" s="142"/>
-      <c r="L57" s="142"/>
-      <c r="M57" s="150"/>
-      <c r="N57" s="142"/>
-      <c r="O57" s="142"/>
-      <c r="P57" s="142"/>
-    </row>
-    <row r="58" spans="9:16" ht="15.75">
-      <c r="I58" s="142"/>
-      <c r="J58" s="142"/>
-      <c r="K58" s="142"/>
-      <c r="L58" s="142"/>
-      <c r="M58" s="150"/>
-      <c r="N58" s="142"/>
-      <c r="O58" s="142"/>
-      <c r="P58" s="142"/>
-    </row>
-    <row r="59" spans="9:16" ht="15.75">
-      <c r="I59" s="142"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="142"/>
-      <c r="L59" s="142"/>
-      <c r="M59" s="150"/>
-      <c r="N59" s="142"/>
-      <c r="O59" s="142"/>
-      <c r="P59" s="142"/>
-    </row>
-    <row r="60" spans="9:16" ht="15.75">
-      <c r="I60" s="142"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="142"/>
-      <c r="L60" s="142"/>
-      <c r="M60" s="142"/>
-      <c r="N60" s="142"/>
-      <c r="O60" s="142"/>
-      <c r="P60" s="142"/>
-    </row>
-    <row r="61" spans="9:16" ht="15.75">
-      <c r="I61" s="142"/>
-      <c r="J61" s="150"/>
-      <c r="K61" s="142"/>
-      <c r="L61" s="142"/>
-      <c r="M61" s="142"/>
-      <c r="N61" s="142"/>
-      <c r="O61" s="142"/>
-      <c r="P61" s="142"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEE55EF-D242-474C-945C-154F43D5E9E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BB8938-351B-48E0-8DEA-9578DE0B6630}">
   <dimension ref="B11:V29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -8324,589 +7941,589 @@
   <sheetData>
     <row r="11" spans="2:22" ht="17.25" thickBot="1">
       <c r="B11" s="123" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="L11" s="123" t="s">
-        <v>168</v>
-      </c>
-      <c r="N11" s="151"/>
-      <c r="O11" s="151"/>
-      <c r="P11" s="151"/>
-      <c r="Q11" s="151"/>
+        <v>170</v>
+      </c>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
     </row>
     <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
-      <c r="B12" s="152" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="152" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="152" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="152" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" s="152" t="s">
-        <v>170</v>
-      </c>
-      <c r="G12" s="152" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="152" t="s">
+      <c r="B12" s="138" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="138" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="138" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="K12" s="152" t="s">
-        <v>91</v>
-      </c>
-      <c r="L12" s="152" t="s">
-        <v>90</v>
-      </c>
-      <c r="M12" s="152" t="s">
+      <c r="F12" s="138" t="s">
         <v>172</v>
       </c>
-      <c r="N12" s="152" t="s">
+      <c r="G12" s="138" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="O12" s="152" t="s">
+      <c r="K12" s="138" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" s="138" t="s">
+        <v>124</v>
+      </c>
+      <c r="M12" s="138" t="s">
         <v>174</v>
       </c>
-      <c r="P12" s="152">
+      <c r="N12" s="138" t="s">
+        <v>175</v>
+      </c>
+      <c r="O12" s="138" t="s">
+        <v>176</v>
+      </c>
+      <c r="P12" s="138">
         <v>2022</v>
       </c>
-      <c r="Q12" s="152">
+      <c r="Q12" s="138">
         <v>0</v>
       </c>
-      <c r="R12" s="152" t="s">
-        <v>59</v>
-      </c>
-      <c r="S12" s="152" t="s">
-        <v>175</v>
+      <c r="R12" s="138" t="s">
+        <v>93</v>
+      </c>
+      <c r="S12" s="138" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="151" t="s">
-        <v>176</v>
-      </c>
-      <c r="C13" s="151" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" s="151" t="s">
-        <v>18</v>
+      <c r="B13" s="137" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="137" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="151" t="str">
+        <v>82</v>
+      </c>
+      <c r="J13" s="137" t="str">
         <f>C13</f>
         <v>ElcAgg_Solar</v>
       </c>
-      <c r="L13" s="151" t="s">
-        <v>102</v>
-      </c>
-      <c r="M13" s="151">
-        <v>1</v>
-      </c>
-      <c r="N13" s="151">
+      <c r="L13" s="137" t="s">
+        <v>136</v>
+      </c>
+      <c r="M13" s="137">
+        <v>1</v>
+      </c>
+      <c r="N13" s="137">
         <v>8.76</v>
       </c>
-      <c r="O13" s="151"/>
-      <c r="P13" s="151"/>
-      <c r="Q13" s="151"/>
+      <c r="O13" s="137"/>
+      <c r="P13" s="137"/>
+      <c r="Q13" s="137"/>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="151" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="151" t="s">
+      <c r="B14" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="151" t="s">
-        <v>18</v>
+      <c r="C14" s="137" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
-      </c>
-      <c r="H14" s="151"/>
-      <c r="I14" s="151"/>
-      <c r="J14" s="151" t="str">
+        <v>82</v>
+      </c>
+      <c r="H14" s="137"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="137" t="str">
         <f>C14</f>
         <v>ElcAgg_Wind</v>
       </c>
-      <c r="L14" s="151" t="s">
-        <v>102</v>
-      </c>
-      <c r="M14" s="151">
-        <v>1</v>
-      </c>
-      <c r="N14" s="151">
+      <c r="L14" s="137" t="s">
+        <v>136</v>
+      </c>
+      <c r="M14" s="137">
+        <v>1</v>
+      </c>
+      <c r="N14" s="137">
         <v>8.76</v>
       </c>
-      <c r="O14" s="151"/>
-      <c r="P14" s="151"/>
-      <c r="Q14" s="151"/>
+      <c r="O14" s="137"/>
+      <c r="P14" s="137"/>
+      <c r="Q14" s="137"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D15" s="151" t="s">
-        <v>181</v>
-      </c>
-      <c r="E15" s="151" t="s">
-        <v>18</v>
+        <v>182</v>
+      </c>
+      <c r="D15" s="137" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="151"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="151"/>
-      <c r="J15" s="151" t="str">
+        <v>21</v>
+      </c>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="137" t="str">
         <f>C15</f>
         <v>e_demand</v>
       </c>
-      <c r="K15" s="151"/>
+      <c r="K15" s="137"/>
       <c r="L15" t="s">
-        <v>182</v>
-      </c>
-      <c r="M15" s="151">
-        <v>1</v>
-      </c>
-      <c r="N15" s="151">
+        <v>184</v>
+      </c>
+      <c r="M15" s="137">
+        <v>1</v>
+      </c>
+      <c r="N15" s="137">
         <v>8.76</v>
       </c>
-      <c r="O15" s="151"/>
-      <c r="P15" s="151"/>
-      <c r="Q15" s="151"/>
+      <c r="O15" s="137"/>
+      <c r="P15" s="137"/>
+      <c r="Q15" s="137"/>
       <c r="V15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="151" t="s">
-        <v>185</v>
-      </c>
-      <c r="E16" s="151" t="s">
-        <v>18</v>
+        <v>186</v>
+      </c>
+      <c r="D16" s="137" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151" t="str">
+        <v>21</v>
+      </c>
+      <c r="G16" s="137"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137" t="str">
         <f>C16</f>
         <v>h2_demand</v>
       </c>
-      <c r="K16" s="151" t="s">
-        <v>101</v>
+      <c r="K16" s="137" t="s">
+        <v>135</v>
       </c>
       <c r="L16" t="s">
-        <v>186</v>
-      </c>
-      <c r="M16" s="151">
-        <v>1</v>
-      </c>
-      <c r="N16" s="151">
+        <v>188</v>
+      </c>
+      <c r="M16" s="137">
+        <v>1</v>
+      </c>
+      <c r="N16" s="137">
         <v>8.76</v>
       </c>
-      <c r="O16" s="151"/>
-      <c r="P16" s="151"/>
-      <c r="Q16" s="151"/>
+      <c r="O16" s="137"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="137"/>
     </row>
     <row r="17" spans="2:22">
       <c r="B17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" s="151" t="s">
-        <v>18</v>
+        <v>190</v>
+      </c>
+      <c r="E17" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="151"/>
+        <v>21</v>
+      </c>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="137"/>
       <c r="J17" t="str">
         <f>C17</f>
         <v>h_demand</v>
       </c>
-      <c r="K17" s="151"/>
+      <c r="K17" s="137"/>
       <c r="L17" t="s">
-        <v>189</v>
-      </c>
-      <c r="M17" s="151">
-        <v>1</v>
-      </c>
-      <c r="N17" s="151">
+        <v>191</v>
+      </c>
+      <c r="M17" s="137">
+        <v>1</v>
+      </c>
+      <c r="N17" s="137">
         <v>8.76</v>
       </c>
-      <c r="O17" s="151"/>
-      <c r="P17" s="151"/>
-      <c r="Q17" s="151"/>
+      <c r="O17" s="137"/>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="137"/>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="151"/>
-      <c r="E18" s="151" t="s">
-        <v>18</v>
+        <v>193</v>
+      </c>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="151"/>
-      <c r="I18" s="151"/>
-      <c r="J18" s="151" t="str">
+        <v>82</v>
+      </c>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137" t="str">
         <f>C20</f>
         <v>fossil_supply</v>
       </c>
-      <c r="K18" s="151"/>
-      <c r="L18" s="151" t="s">
-        <v>49</v>
-      </c>
-      <c r="M18" s="151"/>
-      <c r="N18" s="151"/>
-      <c r="O18" s="151">
+      <c r="K18" s="137"/>
+      <c r="L18" s="137" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="137"/>
+      <c r="N18" s="137"/>
+      <c r="O18" s="137">
         <f t="shared" ref="O18:O22" si="0">V18*3.6</f>
         <v>7.2</v>
       </c>
-      <c r="P18" s="151"/>
-      <c r="V18" s="151">
+      <c r="P18" s="137"/>
+      <c r="V18" s="137">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:22">
       <c r="B19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D19" s="151"/>
-      <c r="E19" s="151" t="s">
-        <v>18</v>
+        <v>195</v>
+      </c>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="151"/>
-      <c r="I19" s="151"/>
-      <c r="K19" s="151"/>
-      <c r="L19" s="151" t="s">
-        <v>13</v>
-      </c>
-      <c r="M19" s="151"/>
-      <c r="N19" s="151"/>
-      <c r="O19" s="151">
+        <v>82</v>
+      </c>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="137"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="P19" s="151"/>
-      <c r="V19" s="151">
+      <c r="P19" s="137"/>
+      <c r="V19" s="137">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="151" t="s">
-        <v>190</v>
-      </c>
-      <c r="C20" s="151" t="s">
-        <v>194</v>
-      </c>
-      <c r="D20" s="151" t="s">
-        <v>195</v>
-      </c>
-      <c r="E20" s="151" t="s">
-        <v>18</v>
+      <c r="B20" s="137" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="137" t="s">
+        <v>197</v>
+      </c>
+      <c r="E20" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="151"/>
-      <c r="H20" s="151"/>
-      <c r="I20" s="151"/>
-      <c r="K20" s="151"/>
-      <c r="L20" s="151" t="s">
-        <v>196</v>
-      </c>
-      <c r="M20" s="151"/>
-      <c r="N20" s="151"/>
-      <c r="O20" s="151">
+        <v>21</v>
+      </c>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137" t="s">
+        <v>198</v>
+      </c>
+      <c r="M20" s="137"/>
+      <c r="N20" s="137"/>
+      <c r="O20" s="137">
         <f>V20*3.6</f>
         <v>36</v>
       </c>
-      <c r="P20" s="151"/>
+      <c r="P20" s="137"/>
       <c r="V20">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:22">
-      <c r="B21" s="151" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="151" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="151" t="s">
-        <v>198</v>
-      </c>
-      <c r="E21" s="151" t="s">
-        <v>18</v>
+      <c r="B21" s="137" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="137" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="137" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="151"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151" t="str">
+        <v>21</v>
+      </c>
+      <c r="G21" s="137"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="137" t="str">
         <f>C21</f>
         <v>renewable</v>
       </c>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151" t="s">
-        <v>199</v>
-      </c>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="151">
+      <c r="K21" s="137"/>
+      <c r="L21" s="137" t="s">
+        <v>201</v>
+      </c>
+      <c r="M21" s="137"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="137">
         <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P21" s="151"/>
+      <c r="P21" s="137"/>
       <c r="V21">
         <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="B22" s="151" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="151" t="s">
-        <v>200</v>
-      </c>
-      <c r="D22" s="151" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="151" t="s">
-        <v>18</v>
+      <c r="B22" s="137" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="137" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="137" t="s">
+        <v>203</v>
+      </c>
+      <c r="E22" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="151"/>
-      <c r="H22" s="151"/>
-      <c r="I22" s="151"/>
-      <c r="K22" s="151"/>
-      <c r="L22" s="151" t="s">
-        <v>202</v>
-      </c>
-      <c r="M22" s="151"/>
-      <c r="N22" s="151"/>
-      <c r="O22" s="151">
+        <v>21</v>
+      </c>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137" t="s">
+        <v>204</v>
+      </c>
+      <c r="M22" s="137"/>
+      <c r="N22" s="137"/>
+      <c r="O22" s="137">
         <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P22" s="151"/>
+      <c r="P22" s="137"/>
       <c r="V22">
         <v>0.1</v>
       </c>
     </row>
     <row r="23" spans="2:22">
-      <c r="B23" s="151" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="151" t="s">
-        <v>203</v>
-      </c>
-      <c r="D23" s="151" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="151" t="s">
-        <v>18</v>
+      <c r="B23" s="137" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="137" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="137" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="151"/>
-      <c r="H23" s="151"/>
-      <c r="I23" s="151"/>
-      <c r="L23" s="151" t="s">
-        <v>51</v>
-      </c>
-      <c r="M23" s="151"/>
-      <c r="N23" s="151"/>
-      <c r="O23" s="151">
+        <v>21</v>
+      </c>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="L23" s="137" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="137"/>
+      <c r="N23" s="137"/>
+      <c r="O23" s="137">
         <f>V23*3.6</f>
         <v>25.2</v>
       </c>
-      <c r="P23" s="151"/>
-      <c r="V23" s="151">
+      <c r="P23" s="137"/>
+      <c r="V23" s="137">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="2:22">
-      <c r="B24" s="151" t="s">
-        <v>190</v>
+      <c r="B24" s="137" t="s">
+        <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D24" t="s">
-        <v>206</v>
-      </c>
-      <c r="E24" s="151" t="s">
-        <v>18</v>
+        <v>208</v>
+      </c>
+      <c r="E24" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="151"/>
-      <c r="H24" s="151"/>
-      <c r="I24" s="151"/>
-      <c r="J24" s="151" t="str">
+        <v>21</v>
+      </c>
+      <c r="G24" s="137"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="137" t="str">
         <f>C22</f>
         <v>nuclear_fuel</v>
       </c>
-      <c r="K24" s="151"/>
-      <c r="L24" s="151" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="151"/>
-      <c r="N24" s="151"/>
-      <c r="O24" s="151">
+      <c r="K24" s="137"/>
+      <c r="L24" s="137" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24" s="137"/>
+      <c r="N24" s="137"/>
+      <c r="O24" s="137">
         <f>V24*3.6</f>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P24" s="151"/>
+      <c r="P24" s="137"/>
       <c r="V24">
         <v>0.1</v>
       </c>
     </row>
     <row r="25" spans="2:22">
-      <c r="B25" s="151" t="s">
-        <v>190</v>
+      <c r="B25" s="137" t="s">
+        <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="151" t="s">
-        <v>18</v>
+        <v>210</v>
+      </c>
+      <c r="E25" s="137" t="s">
+        <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="151"/>
-      <c r="H25" s="151"/>
-      <c r="I25" s="151"/>
-      <c r="J25" s="151" t="str">
+        <v>21</v>
+      </c>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137" t="str">
         <f>C23</f>
         <v>solar_potential</v>
       </c>
-      <c r="K25" s="151"/>
-      <c r="L25" s="151" t="s">
-        <v>209</v>
-      </c>
-      <c r="M25" s="151"/>
-      <c r="N25" s="151"/>
-      <c r="O25" s="151">
+      <c r="K25" s="137"/>
+      <c r="L25" s="137" t="s">
+        <v>211</v>
+      </c>
+      <c r="M25" s="137"/>
+      <c r="N25" s="137"/>
+      <c r="O25" s="137">
         <f>V25*3.6</f>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P25" s="151"/>
+      <c r="P25" s="137"/>
       <c r="V25">
         <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="2:22">
-      <c r="B26" s="151"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="151"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="151"/>
-      <c r="G26" s="151"/>
-      <c r="H26" s="151"/>
-      <c r="I26" s="151"/>
-      <c r="J26" s="151" t="str">
+      <c r="B26" s="137"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="137" t="str">
         <f>C24</f>
         <v>winon_potential</v>
       </c>
-      <c r="K26" s="151"/>
-      <c r="L26" s="151" t="s">
-        <v>210</v>
-      </c>
-      <c r="M26" s="151"/>
-      <c r="N26" s="151"/>
-      <c r="O26" s="151">
+      <c r="K26" s="137"/>
+      <c r="L26" s="137" t="s">
+        <v>212</v>
+      </c>
+      <c r="M26" s="137"/>
+      <c r="N26" s="137"/>
+      <c r="O26" s="137">
         <f>V26*3.6</f>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P26" s="151"/>
+      <c r="P26" s="137"/>
       <c r="V26">
         <v>0.1</v>
       </c>
     </row>
     <row r="27" spans="2:22">
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
-      <c r="H27" s="151"/>
-      <c r="I27" s="151"/>
-      <c r="J27" s="151" t="str">
+      <c r="B27" s="137"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="137"/>
+      <c r="J27" s="137" t="str">
         <f>C25</f>
         <v>winoff_potential</v>
       </c>
-      <c r="K27" s="151"/>
-      <c r="L27" s="151" t="s">
-        <v>211</v>
-      </c>
-      <c r="M27" s="151"/>
-      <c r="N27" s="151"/>
-      <c r="O27" s="151">
+      <c r="K27" s="137"/>
+      <c r="L27" s="137" t="s">
+        <v>213</v>
+      </c>
+      <c r="M27" s="137"/>
+      <c r="N27" s="137"/>
+      <c r="O27" s="137">
         <f t="shared" ref="O27" si="1">V27*3.6</f>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P27" s="151"/>
+      <c r="P27" s="137"/>
       <c r="V27">
         <v>0.1</v>
       </c>
@@ -8954,8 +8571,8 @@
       <c r="S29">
         <v>50</v>
       </c>
-      <c r="V29" s="153" t="s">
-        <v>14</v>
+      <c r="V29" s="139" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
